--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 днрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\15,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD5F40-A60A-4721-8700-6BEA31D5D460}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA3A2B-BD10-4327-ACFE-B94BE409A23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AN$138</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -854,7 +846,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -874,9 +866,7 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -897,7 +887,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Лист1"/>
@@ -1375,15 +1365,16 @@
     <col min="19" max="20" width="7" customWidth="1"/>
     <col min="21" max="21" width="5" customWidth="1"/>
     <col min="22" max="26" width="7" customWidth="1"/>
-    <col min="27" max="27" width="7" style="21" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" style="21" customWidth="1"/>
+    <col min="27" max="27" width="7" style="19" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" style="19" customWidth="1"/>
     <col min="29" max="30" width="5" customWidth="1"/>
     <col min="31" max="33" width="7" customWidth="1"/>
     <col min="34" max="34" width="6" customWidth="1"/>
     <col min="35" max="38" width="6.7109375" customWidth="1"/>
-    <col min="39" max="39" width="13.7109375" customWidth="1"/>
+    <col min="39" max="39" width="7.85546875" customWidth="1"/>
     <col min="40" max="41" width="7" customWidth="1"/>
-    <col min="42" max="48" width="3" customWidth="1"/>
+    <col min="42" max="42" width="7.85546875" customWidth="1"/>
+    <col min="43" max="48" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -1412,7 +1403,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="22">
+      <c r="Z1" s="20">
         <v>0.57479999999999998</v>
       </c>
       <c r="AA1" s="1"/>
@@ -1844,7 +1835,10 @@
         <f>SUM(AO6:AO500)</f>
         <v>17599</v>
       </c>
-      <c r="AP5" s="1"/>
+      <c r="AP5" s="4">
+        <f>SUM(AP6:AP500)</f>
+        <v>9990.647930000001</v>
+      </c>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
       <c r="AS5" s="1"/>
@@ -1925,10 +1919,10 @@
         <f>X6*$Z$1</f>
         <v>1034.6399999999999</v>
       </c>
-      <c r="AA6" s="19">
+      <c r="AA6" s="1">
         <v>2000</v>
       </c>
-      <c r="AB6" s="19" t="str">
+      <c r="AB6" s="1" t="str">
         <f>VLOOKUP(A6,[1]Лист1!$A:$B,2,0)</f>
         <v>2000 кг (акция сентябрь)</v>
       </c>
@@ -1973,7 +1967,10 @@
         <f>ROUND(G6*Z6,0)</f>
         <v>1035</v>
       </c>
-      <c r="AP6" s="1"/>
+      <c r="AP6" s="1">
+        <f>V6*G6</f>
+        <v>330.37540000000001</v>
+      </c>
       <c r="AQ6" s="1"/>
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
@@ -2053,8 +2050,8 @@
         <f t="shared" ref="Z7:Z8" si="10">X7*$Z$1</f>
         <v>1116.4627799999998</v>
       </c>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
       <c r="AC7" s="1">
         <f t="shared" ref="AC7:AC70" si="11">(F7+O7+P7+Q7+R7+S7+T7+U7+X7)/V7</f>
         <v>11</v>
@@ -2098,7 +2095,10 @@
         <f t="shared" ref="AO7:AO70" si="13">ROUND(G7*Z7,0)</f>
         <v>1116</v>
       </c>
-      <c r="AP7" s="1"/>
+      <c r="AP7" s="1">
+        <f t="shared" ref="AP7:AP70" si="14">V7*G7</f>
+        <v>367.75</v>
+      </c>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="1"/>
       <c r="AS7" s="1"/>
@@ -2178,8 +2178,8 @@
         <f t="shared" si="10"/>
         <v>1796.2755211200006</v>
       </c>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
       <c r="AC8" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -2223,7 +2223,10 @@
         <f t="shared" si="13"/>
         <v>1796</v>
       </c>
-      <c r="AP8" s="1"/>
+      <c r="AP8" s="1">
+        <f t="shared" si="14"/>
+        <v>833.0154</v>
+      </c>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
@@ -2293,8 +2296,8 @@
         <v>0</v>
       </c>
       <c r="Z9" s="5"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
       <c r="AC9" s="1">
         <f t="shared" si="11"/>
         <v>137.99999999999997</v>
@@ -2338,7 +2341,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="1"/>
+      <c r="AP9" s="1">
+        <f t="shared" si="14"/>
+        <v>8.0000000000000016E-2</v>
+      </c>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1"/>
@@ -2415,11 +2421,11 @@
         <v>299.83675328000004</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" ref="Z10:Z11" si="14">X10*$Z$1</f>
+        <f t="shared" ref="Z10:Z11" si="15">X10*$Z$1</f>
         <v>405.32964672000003</v>
       </c>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
       <c r="AC10" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -2461,7 +2467,10 @@
         <f t="shared" si="13"/>
         <v>182</v>
       </c>
-      <c r="AP10" s="1"/>
+      <c r="AP10" s="1">
+        <f t="shared" si="14"/>
+        <v>238.89023999999998</v>
+      </c>
       <c r="AQ10" s="1"/>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
@@ -2540,11 +2549,11 @@
         <v>255.18981783999971</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>344.97438215999955</v>
       </c>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
       <c r="AC11" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -2588,7 +2597,10 @@
         <f t="shared" si="13"/>
         <v>155</v>
       </c>
-      <c r="AP11" s="1"/>
+      <c r="AP11" s="1">
+        <f t="shared" si="14"/>
+        <v>257.70429000000001</v>
+      </c>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
       <c r="AS11" s="1"/>
@@ -2664,8 +2676,8 @@
         <v>0</v>
       </c>
       <c r="Z12" s="5"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
       <c r="AC12" s="1">
         <f t="shared" si="11"/>
         <v>20.74468085106383</v>
@@ -2707,7 +2719,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="1"/>
+      <c r="AP12" s="1">
+        <f t="shared" si="14"/>
+        <v>1.5980000000000001</v>
+      </c>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
@@ -2784,8 +2799,8 @@
         <v>18.299999999999997</v>
       </c>
       <c r="Z13" s="5"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
       <c r="AC13" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -2827,7 +2842,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="1"/>
+      <c r="AP13" s="1">
+        <f t="shared" si="14"/>
+        <v>2.76</v>
+      </c>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1"/>
@@ -2902,8 +2920,8 @@
         <v>59.039999999999736</v>
       </c>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
       <c r="AC14" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -2945,7 +2963,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="1"/>
+      <c r="AP14" s="1">
+        <f t="shared" si="14"/>
+        <v>5.5759999999999996</v>
+      </c>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
@@ -3011,8 +3032,8 @@
         <v>0</v>
       </c>
       <c r="Z15" s="5"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="19"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="1"/>
       <c r="AC15" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -3056,7 +3077,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="1"/>
+      <c r="AP15" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
@@ -3121,7 +3145,7 @@
         <v>934.93299999999999</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" ref="W16" si="15">11*V16-U16-T16-S16-R16-Q16-P16-O16-F16</f>
+        <f t="shared" ref="W16" si="16">11*V16-U16-T16-S16-R16-Q16-P16-O16-F16</f>
         <v>3619.0079999999989</v>
       </c>
       <c r="X16" s="5">
@@ -3133,11 +3157,11 @@
         <v>1538.8022015999995</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" ref="Z16:Z17" si="16">X16*$Z$1</f>
+        <f t="shared" ref="Z16:Z17" si="17">X16*$Z$1</f>
         <v>2080.2057983999994</v>
       </c>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
       <c r="AC16" s="1">
         <f t="shared" si="11"/>
         <v>10.999999999999998</v>
@@ -3181,7 +3205,10 @@
         <f t="shared" si="13"/>
         <v>2080</v>
       </c>
-      <c r="AP16" s="1"/>
+      <c r="AP16" s="1">
+        <f t="shared" si="14"/>
+        <v>934.93299999999999</v>
+      </c>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
@@ -3259,13 +3286,13 @@
         <v>595.28000000000009</v>
       </c>
       <c r="Z17" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>804.71999999999991</v>
       </c>
-      <c r="AA17" s="19">
+      <c r="AA17" s="1">
         <v>2000</v>
       </c>
-      <c r="AB17" s="19" t="str">
+      <c r="AB17" s="1" t="str">
         <f>VLOOKUP(A17,[1]Лист1!$A:$B,2,0)</f>
         <v>2000 кг  (акция сентябрь)</v>
       </c>
@@ -3312,7 +3339,10 @@
         <f t="shared" si="13"/>
         <v>805</v>
       </c>
-      <c r="AP17" s="1"/>
+      <c r="AP17" s="1">
+        <f t="shared" si="14"/>
+        <v>778.13599999999997</v>
+      </c>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
@@ -3384,8 +3414,8 @@
         <v>0</v>
       </c>
       <c r="Z18" s="5"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
       <c r="AC18" s="1">
         <f t="shared" si="11"/>
         <v>25.870477985853608</v>
@@ -3427,7 +3457,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="1"/>
+      <c r="AP18" s="1">
+        <f t="shared" si="14"/>
+        <v>25.674400000000002</v>
+      </c>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
@@ -3491,8 +3524,8 @@
         <v>0</v>
       </c>
       <c r="Z19" s="5"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="19"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="1"/>
       <c r="AC19" s="1">
         <f t="shared" si="11"/>
         <v>-5.8470588235294114</v>
@@ -3534,7 +3567,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="1"/>
+      <c r="AP19" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
@@ -3594,8 +3630,8 @@
         <v>0</v>
       </c>
       <c r="Z20" s="5"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="19"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="1"/>
       <c r="AC20" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -3639,7 +3675,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="1"/>
+      <c r="AP20" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
@@ -3711,8 +3750,8 @@
         <v>0</v>
       </c>
       <c r="Z21" s="5"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
       <c r="AC21" s="1">
         <f t="shared" si="11"/>
         <v>17.11776187378009</v>
@@ -3754,7 +3793,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="1"/>
+      <c r="AP21" s="1">
+        <f t="shared" si="14"/>
+        <v>0.92219999999999991</v>
+      </c>
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
@@ -3821,7 +3863,7 @@
         <v>804.43240000000003</v>
       </c>
       <c r="W22" s="5">
-        <f t="shared" ref="W22" si="17">11*V22-U22-T22-S22-R22-Q22-P22-O22-F22</f>
+        <f t="shared" ref="W22" si="18">11*V22-U22-T22-S22-R22-Q22-P22-O22-F22</f>
         <v>1627.6606000000006</v>
       </c>
       <c r="X22" s="5">
@@ -3835,10 +3877,10 @@
         <f>X22*$Z$1</f>
         <v>1149.5999999999999</v>
       </c>
-      <c r="AA22" s="19">
+      <c r="AA22" s="1">
         <v>2500</v>
       </c>
-      <c r="AB22" s="19" t="str">
+      <c r="AB22" s="1" t="str">
         <f>VLOOKUP(A22,[1]Лист1!$A:$B,2,0)</f>
         <v>2500 кг (акция сентябрь)</v>
       </c>
@@ -3883,7 +3925,10 @@
         <f t="shared" si="13"/>
         <v>1150</v>
       </c>
-      <c r="AP22" s="1"/>
+      <c r="AP22" s="1">
+        <f t="shared" si="14"/>
+        <v>804.43240000000003</v>
+      </c>
       <c r="AQ22" s="1"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
@@ -3949,8 +3994,8 @@
         <v>0</v>
       </c>
       <c r="Z23" s="5"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="19"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="1"/>
       <c r="AC23" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -3992,7 +4037,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="1"/>
+      <c r="AP23" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
@@ -4068,8 +4116,8 @@
         <v>0</v>
       </c>
       <c r="Z24" s="5"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
       <c r="AC24" s="1">
         <f t="shared" si="11"/>
         <v>20.556254668506039</v>
@@ -4113,7 +4161,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP24" s="1"/>
+      <c r="AP24" s="1">
+        <f t="shared" si="14"/>
+        <v>51.611799999999995</v>
+      </c>
       <c r="AQ24" s="1"/>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
@@ -4178,7 +4229,7 @@
         <v>285.91019999999997</v>
       </c>
       <c r="W25" s="5">
-        <f t="shared" ref="W25" si="18">11*V25-U25-T25-S25-R25-Q25-P25-O25-F25</f>
+        <f t="shared" ref="W25" si="19">11*V25-U25-T25-S25-R25-Q25-P25-O25-F25</f>
         <v>949.24979999999982</v>
       </c>
       <c r="X25" s="5">
@@ -4193,8 +4244,8 @@
         <f>X25*$Z$1</f>
         <v>545.62878503999991</v>
       </c>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
       <c r="AC25" s="1">
         <f t="shared" si="11"/>
         <v>11.000000000000002</v>
@@ -4238,7 +4289,10 @@
         <f t="shared" si="13"/>
         <v>546</v>
       </c>
-      <c r="AP25" s="1"/>
+      <c r="AP25" s="1">
+        <f t="shared" si="14"/>
+        <v>285.91019999999997</v>
+      </c>
       <c r="AQ25" s="1"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
@@ -4300,8 +4354,8 @@
         <v>0</v>
       </c>
       <c r="Z26" s="5"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="19"/>
+      <c r="AA26" s="11"/>
+      <c r="AB26" s="1"/>
       <c r="AC26" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -4345,7 +4399,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP26" s="1"/>
+      <c r="AP26" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
@@ -4410,7 +4467,7 @@
         <v>537.15940000000001</v>
       </c>
       <c r="W27" s="5">
-        <f t="shared" ref="W27" si="19">11*V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
+        <f t="shared" ref="W27" si="20">11*V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
         <v>2289.2029999999991</v>
       </c>
       <c r="X27" s="5">
@@ -4425,8 +4482,8 @@
         <f>X27*$Z$1</f>
         <v>1315.8338843999993</v>
       </c>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="19"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
       <c r="AC27" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
@@ -4470,7 +4527,10 @@
         <f t="shared" si="13"/>
         <v>1316</v>
       </c>
-      <c r="AP27" s="1"/>
+      <c r="AP27" s="1">
+        <f t="shared" si="14"/>
+        <v>537.15940000000001</v>
+      </c>
       <c r="AQ27" s="1"/>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1"/>
@@ -4544,8 +4604,8 @@
         <v>0</v>
       </c>
       <c r="Z28" s="5"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="19"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
       <c r="AC28" s="1">
         <f t="shared" si="11"/>
         <v>30.88600874453466</v>
@@ -4589,7 +4649,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="1"/>
+      <c r="AP28" s="1">
+        <f t="shared" si="14"/>
+        <v>1.6010000000000002</v>
+      </c>
       <c r="AQ28" s="1"/>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1"/>
@@ -4653,8 +4716,8 @@
         <v>0</v>
       </c>
       <c r="Z29" s="5"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="19"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="1"/>
       <c r="AC29" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -4696,7 +4759,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP29" s="1"/>
+      <c r="AP29" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
       <c r="AS29" s="1"/>
@@ -4756,8 +4822,8 @@
         <v>0</v>
       </c>
       <c r="Z30" s="5"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="19"/>
+      <c r="AA30" s="11"/>
+      <c r="AB30" s="1"/>
       <c r="AC30" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -4801,7 +4867,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP30" s="1"/>
+      <c r="AP30" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ30" s="1"/>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
@@ -4861,8 +4930,8 @@
         <v>0</v>
       </c>
       <c r="Z31" s="5"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="19"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="1"/>
       <c r="AC31" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -4906,7 +4975,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP31" s="1"/>
+      <c r="AP31" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
@@ -4987,10 +5059,10 @@
         <f>X32*$Z$1</f>
         <v>747.24</v>
       </c>
-      <c r="AA32" s="19">
+      <c r="AA32" s="1">
         <v>1500</v>
       </c>
-      <c r="AB32" s="19" t="str">
+      <c r="AB32" s="1" t="str">
         <f>VLOOKUP(A32,[1]Лист1!$A:$B,2,0)</f>
         <v>1500 кг</v>
       </c>
@@ -5037,7 +5109,10 @@
         <f t="shared" si="13"/>
         <v>747</v>
       </c>
-      <c r="AP32" s="1"/>
+      <c r="AP32" s="1">
+        <f t="shared" si="14"/>
+        <v>231.65859999999998</v>
+      </c>
       <c r="AQ32" s="1"/>
       <c r="AR32" s="1"/>
       <c r="AS32" s="1"/>
@@ -5105,8 +5180,8 @@
         <v>0</v>
       </c>
       <c r="Z33" s="5"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="19"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="1"/>
       <c r="AC33" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -5148,7 +5223,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP33" s="1"/>
+      <c r="AP33" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
@@ -5228,8 +5306,8 @@
         <f>X34*$Z$1</f>
         <v>1149.5999999999999</v>
       </c>
-      <c r="AA34" s="19"/>
-      <c r="AB34" s="19"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
       <c r="AC34" s="1">
         <f t="shared" si="11"/>
         <v>31.554226729920526</v>
@@ -5273,7 +5351,10 @@
         <f t="shared" si="13"/>
         <v>1150</v>
       </c>
-      <c r="AP34" s="1"/>
+      <c r="AP34" s="1">
+        <f t="shared" si="14"/>
+        <v>192.2834</v>
+      </c>
       <c r="AQ34" s="1"/>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1"/>
@@ -5333,8 +5414,8 @@
         <v>0</v>
       </c>
       <c r="Z35" s="5"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="19"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="1"/>
       <c r="AC35" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -5378,7 +5459,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="1"/>
+      <c r="AP35" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
@@ -5438,8 +5522,8 @@
         <v>0</v>
       </c>
       <c r="Z36" s="5"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="19"/>
+      <c r="AA36" s="11"/>
+      <c r="AB36" s="1"/>
       <c r="AC36" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -5483,7 +5567,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP36" s="1"/>
+      <c r="AP36" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ36" s="1"/>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1"/>
@@ -5543,8 +5630,8 @@
         <v>0</v>
       </c>
       <c r="Z37" s="5"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="19"/>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="1"/>
       <c r="AC37" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
@@ -5588,7 +5675,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP37" s="1"/>
+      <c r="AP37" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
@@ -5617,11 +5707,11 @@
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11">
-        <f t="shared" ref="L38:L69" si="20">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="21">E38-K38</f>
         <v>0</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" ref="M38:M69" si="21">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="22">E38-N38</f>
         <v>0</v>
       </c>
       <c r="N38" s="11"/>
@@ -5635,7 +5725,7 @@
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
       <c r="V38" s="11">
-        <f t="shared" ref="V38:V69" si="22">M38/5</f>
+        <f t="shared" ref="V38:V69" si="23">M38/5</f>
         <v>0</v>
       </c>
       <c r="W38" s="13"/>
@@ -5648,14 +5738,14 @@
         <v>0</v>
       </c>
       <c r="Z38" s="5"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="19"/>
+      <c r="AA38" s="11"/>
+      <c r="AB38" s="1"/>
       <c r="AC38" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD38" s="11" t="e">
-        <f t="shared" ref="AD38:AD69" si="23">(F38+O38+P38+Q38+R38+S38+T38+U38)/V38</f>
+        <f t="shared" ref="AD38:AD69" si="24">(F38+O38+P38+Q38+R38+S38+T38+U38)/V38</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE38" s="11">
@@ -5693,7 +5783,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP38" s="1"/>
+      <c r="AP38" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ38" s="1"/>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1"/>
@@ -5734,11 +5827,11 @@
         <v>5213</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-788</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4347</v>
       </c>
       <c r="N39" s="1">
@@ -5756,11 +5849,11 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>869.4</v>
       </c>
       <c r="W39" s="5">
-        <f t="shared" ref="W39:W49" si="24">11*V39-U39-T39-S39-R39-Q39-P39-O39-F39</f>
+        <f t="shared" ref="W39:W49" si="25">11*V39-U39-T39-S39-R39-Q39-P39-O39-F39</f>
         <v>3512.3999999999996</v>
       </c>
       <c r="X39" s="5">
@@ -5774,14 +5867,14 @@
         <f>X39*$Z$1</f>
         <v>1724.3999999999999</v>
       </c>
-      <c r="AA39" s="19"/>
-      <c r="AB39" s="19"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
       <c r="AC39" s="1">
         <f t="shared" si="11"/>
         <v>10.410628019323672</v>
       </c>
       <c r="AD39" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.9599723947550034</v>
       </c>
       <c r="AE39" s="1">
@@ -5819,7 +5912,10 @@
         <f t="shared" si="13"/>
         <v>690</v>
       </c>
-      <c r="AP39" s="1"/>
+      <c r="AP39" s="1">
+        <f t="shared" si="14"/>
+        <v>347.76</v>
+      </c>
       <c r="AQ39" s="1"/>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1"/>
@@ -5860,11 +5956,11 @@
         <v>1720</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1300</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>420</v>
       </c>
       <c r="N40" s="1"/>
@@ -5880,7 +5976,7 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="W40" s="5"/>
@@ -5893,14 +5989,14 @@
         <v>0</v>
       </c>
       <c r="Z40" s="5"/>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
       <c r="AC40" s="1">
         <f t="shared" si="11"/>
         <v>12.510328071428571</v>
       </c>
       <c r="AD40" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12.510328071428571</v>
       </c>
       <c r="AE40" s="1">
@@ -5938,7 +6034,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP40" s="1"/>
+      <c r="AP40" s="1">
+        <f t="shared" si="14"/>
+        <v>37.800000000000004</v>
+      </c>
       <c r="AQ40" s="1"/>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1"/>
@@ -5979,11 +6078,11 @@
         <v>1427</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-665</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>762</v>
       </c>
       <c r="N41" s="1"/>
@@ -5999,11 +6098,11 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>152.4</v>
       </c>
       <c r="W41" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>256.00000000000023</v>
       </c>
       <c r="X41" s="5">
@@ -6018,14 +6117,14 @@
         <f>X41*$Z$1</f>
         <v>147.14880000000014</v>
       </c>
-      <c r="AA41" s="19"/>
-      <c r="AB41" s="19"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
       <c r="AC41" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3202099737532791</v>
       </c>
       <c r="AE41" s="1">
@@ -6061,7 +6160,10 @@
         <f t="shared" si="13"/>
         <v>59</v>
       </c>
-      <c r="AP41" s="1"/>
+      <c r="AP41" s="1">
+        <f t="shared" si="14"/>
+        <v>60.960000000000008</v>
+      </c>
       <c r="AQ41" s="1"/>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1"/>
@@ -6102,11 +6204,11 @@
         <v>843</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-775</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>68</v>
       </c>
       <c r="N42" s="1"/>
@@ -6126,7 +6228,7 @@
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.6</v>
       </c>
       <c r="W42" s="5">
@@ -6141,14 +6243,14 @@
         <v>100</v>
       </c>
       <c r="Z42" s="5"/>
-      <c r="AA42" s="19"/>
-      <c r="AB42" s="19"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
       <c r="AC42" s="1">
         <f t="shared" si="11"/>
         <v>5.7352941176470589</v>
       </c>
       <c r="AD42" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-1.6176470588235294</v>
       </c>
       <c r="AE42" s="1">
@@ -6184,7 +6286,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP42" s="1"/>
+      <c r="AP42" s="1">
+        <f t="shared" si="14"/>
+        <v>5.44</v>
+      </c>
       <c r="AQ42" s="1"/>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1"/>
@@ -6223,11 +6328,11 @@
         <v>34.5</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-2.8889999999999993</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>31.611000000000001</v>
       </c>
       <c r="N43" s="1"/>
@@ -6243,7 +6348,7 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.3222000000000005</v>
       </c>
       <c r="W43" s="5"/>
@@ -6256,14 +6361,14 @@
         <v>0</v>
       </c>
       <c r="Z43" s="5"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="19"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
       <c r="AC43" s="1">
         <f t="shared" si="11"/>
         <v>32.312802505456958</v>
       </c>
       <c r="AD43" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>32.312802505456958</v>
       </c>
       <c r="AE43" s="1">
@@ -6301,7 +6406,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP43" s="1"/>
+      <c r="AP43" s="1">
+        <f t="shared" si="14"/>
+        <v>6.3222000000000005</v>
+      </c>
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1"/>
@@ -6342,11 +6450,11 @@
         <v>361</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-81</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>280</v>
       </c>
       <c r="N44" s="1"/>
@@ -6362,7 +6470,7 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>56</v>
       </c>
       <c r="W44" s="5"/>
@@ -6375,10 +6483,10 @@
         <v>200</v>
       </c>
       <c r="Z44" s="5"/>
-      <c r="AA44" s="19">
+      <c r="AA44" s="1">
         <v>200</v>
       </c>
-      <c r="AB44" s="19" t="str">
+      <c r="AB44" s="1" t="str">
         <f>VLOOKUP(A44,[1]Лист1!$A:$B,2,0)</f>
         <v>200 шт (акция сентябрь)</v>
       </c>
@@ -6387,7 +6495,7 @@
         <v>18.521428571428572</v>
       </c>
       <c r="AD44" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.950000000000001</v>
       </c>
       <c r="AE44" s="1">
@@ -6423,7 +6531,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP44" s="1"/>
+      <c r="AP44" s="1">
+        <f t="shared" si="14"/>
+        <v>5.6000000000000005</v>
+      </c>
       <c r="AQ44" s="1"/>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1"/>
@@ -6464,11 +6575,11 @@
         <v>106</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-15</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>91</v>
       </c>
       <c r="N45" s="1"/>
@@ -6484,7 +6595,7 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18.2</v>
       </c>
       <c r="W45" s="5">
@@ -6499,14 +6610,14 @@
         <v>120</v>
       </c>
       <c r="Z45" s="5"/>
-      <c r="AA45" s="19"/>
-      <c r="AB45" s="19"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
       <c r="AC45" s="1">
         <f t="shared" si="11"/>
         <v>6.4285714285714288</v>
       </c>
       <c r="AD45" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-0.16483516483516483</v>
       </c>
       <c r="AE45" s="1">
@@ -6542,7 +6653,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP45" s="1"/>
+      <c r="AP45" s="1">
+        <f t="shared" si="14"/>
+        <v>6.3699999999999992</v>
+      </c>
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1"/>
@@ -6583,11 +6697,11 @@
         <v>29.3</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-10.158000000000001</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19.141999999999999</v>
       </c>
       <c r="N46" s="1"/>
@@ -6603,11 +6717,11 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.8283999999999998</v>
       </c>
       <c r="W46" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>26.244399999999999</v>
       </c>
       <c r="X46" s="5">
@@ -6619,14 +6733,14 @@
         <v>26.244399999999999</v>
       </c>
       <c r="Z46" s="5"/>
-      <c r="AA46" s="19"/>
-      <c r="AB46" s="19"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
       <c r="AC46" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD46" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.1448124542889984</v>
       </c>
       <c r="AE46" s="1">
@@ -6662,7 +6776,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP46" s="1"/>
+      <c r="AP46" s="1">
+        <f t="shared" si="14"/>
+        <v>3.8283999999999998</v>
+      </c>
       <c r="AQ46" s="1"/>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1"/>
@@ -6703,11 +6820,11 @@
         <v>466</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-210</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>256</v>
       </c>
       <c r="N47" s="1"/>
@@ -6723,11 +6840,11 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>51.2</v>
       </c>
       <c r="W47" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>224.60000000000002</v>
       </c>
       <c r="X47" s="5">
@@ -6739,17 +6856,17 @@
         <v>95.499920000000003</v>
       </c>
       <c r="Z47" s="5">
-        <f t="shared" ref="Z47:Z48" si="25">X47*$Z$1</f>
+        <f t="shared" ref="Z47:Z48" si="26">X47*$Z$1</f>
         <v>129.10008000000002</v>
       </c>
-      <c r="AA47" s="19"/>
-      <c r="AB47" s="19"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
       <c r="AC47" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD47" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.61328125</v>
       </c>
       <c r="AE47" s="1">
@@ -6785,7 +6902,10 @@
         <f t="shared" si="13"/>
         <v>52</v>
       </c>
-      <c r="AP47" s="1"/>
+      <c r="AP47" s="1">
+        <f t="shared" si="14"/>
+        <v>20.480000000000004</v>
+      </c>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
@@ -6826,11 +6946,11 @@
         <v>736</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-432</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>304</v>
       </c>
       <c r="N48" s="1"/>
@@ -6848,7 +6968,7 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>60.8</v>
       </c>
       <c r="W48" s="5">
@@ -6863,17 +6983,17 @@
         <v>127.56</v>
       </c>
       <c r="Z48" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>172.44</v>
       </c>
-      <c r="AA48" s="19"/>
-      <c r="AB48" s="19"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
       <c r="AC48" s="1">
         <f t="shared" si="11"/>
         <v>15.304276315789474</v>
       </c>
       <c r="AD48" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.370065789473685</v>
       </c>
       <c r="AE48" s="1">
@@ -6909,7 +7029,10 @@
         <f t="shared" si="13"/>
         <v>69</v>
       </c>
-      <c r="AP48" s="1"/>
+      <c r="AP48" s="1">
+        <f t="shared" si="14"/>
+        <v>24.32</v>
+      </c>
       <c r="AQ48" s="1"/>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
@@ -6950,11 +7073,11 @@
         <v>171.4</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-107.09400000000001</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>64.305999999999997</v>
       </c>
       <c r="N49" s="1"/>
@@ -6968,11 +7091,11 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.8612</v>
       </c>
       <c r="W49" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>40.441199999999995</v>
       </c>
       <c r="X49" s="5">
@@ -6984,14 +7107,14 @@
         <v>40.441199999999995</v>
       </c>
       <c r="Z49" s="5"/>
-      <c r="AA49" s="19"/>
-      <c r="AB49" s="19"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
       <c r="AC49" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD49" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.8555655770845636</v>
       </c>
       <c r="AE49" s="1">
@@ -7029,7 +7152,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP49" s="1"/>
+      <c r="AP49" s="1">
+        <f t="shared" si="14"/>
+        <v>12.8612</v>
+      </c>
       <c r="AQ49" s="1"/>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1"/>
@@ -7070,11 +7196,11 @@
         <v>1545</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-58</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1487</v>
       </c>
       <c r="N50" s="1"/>
@@ -7092,7 +7218,7 @@
       </c>
       <c r="U50" s="1"/>
       <c r="V50" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>297.39999999999998</v>
       </c>
       <c r="W50" s="5">
@@ -7110,10 +7236,10 @@
         <f>X50*$Z$1</f>
         <v>517.31999999999994</v>
       </c>
-      <c r="AA50" s="19">
+      <c r="AA50" s="1">
         <v>900</v>
       </c>
-      <c r="AB50" s="19" t="str">
+      <c r="AB50" s="1" t="str">
         <f>VLOOKUP(A50,[1]Лист1!$A:$B,2,0)</f>
         <v>900 шт</v>
       </c>
@@ -7122,7 +7248,7 @@
         <v>4.4783120376597179</v>
       </c>
       <c r="AD50" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.452084734364492</v>
       </c>
       <c r="AE50" s="1">
@@ -7160,7 +7286,10 @@
         <f t="shared" si="13"/>
         <v>181</v>
       </c>
-      <c r="AP50" s="1"/>
+      <c r="AP50" s="1">
+        <f t="shared" si="14"/>
+        <v>104.08999999999999</v>
+      </c>
       <c r="AQ50" s="1"/>
       <c r="AR50" s="1"/>
       <c r="AS50" s="1"/>
@@ -7201,11 +7330,11 @@
         <v>509</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-49</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>460</v>
       </c>
       <c r="N51" s="1"/>
@@ -7221,7 +7350,7 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>92</v>
       </c>
       <c r="W51" s="5">
@@ -7236,14 +7365,14 @@
         <v>50</v>
       </c>
       <c r="Z51" s="5"/>
-      <c r="AA51" s="19"/>
-      <c r="AB51" s="19"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
       <c r="AC51" s="1">
         <f t="shared" si="11"/>
         <v>11.657608695652174</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.114130434782609</v>
       </c>
       <c r="AE51" s="1">
@@ -7279,7 +7408,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP51" s="1"/>
+      <c r="AP51" s="1">
+        <f t="shared" si="14"/>
+        <v>36.800000000000004</v>
+      </c>
       <c r="AQ51" s="1"/>
       <c r="AR51" s="1"/>
       <c r="AS51" s="1"/>
@@ -7320,11 +7452,11 @@
         <v>154.22399999999999</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-5.8369999999999891</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>148.387</v>
       </c>
       <c r="N52" s="1"/>
@@ -7338,7 +7470,7 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>29.677399999999999</v>
       </c>
       <c r="W52" s="5">
@@ -7354,14 +7486,14 @@
         <v>175.0985</v>
       </c>
       <c r="Z52" s="5"/>
-      <c r="AA52" s="19"/>
-      <c r="AB52" s="19"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
       <c r="AC52" s="1">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="AD52" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.0999379999595655</v>
       </c>
       <c r="AE52" s="1">
@@ -7397,7 +7529,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP52" s="1"/>
+      <c r="AP52" s="1">
+        <f t="shared" si="14"/>
+        <v>29.677399999999999</v>
+      </c>
       <c r="AQ52" s="1"/>
       <c r="AR52" s="1"/>
       <c r="AS52" s="1"/>
@@ -7438,11 +7573,11 @@
         <v>821.298</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-107.20399999999995</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>474.82100000000003</v>
       </c>
       <c r="N53" s="1">
@@ -7460,7 +7595,7 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>94.964200000000005</v>
       </c>
       <c r="W53" s="5">
@@ -7478,10 +7613,10 @@
         <f>X53*$Z$1</f>
         <v>258.65999999999997</v>
       </c>
-      <c r="AA53" s="19">
+      <c r="AA53" s="1">
         <v>450</v>
       </c>
-      <c r="AB53" s="19" t="str">
+      <c r="AB53" s="1" t="str">
         <f>VLOOKUP(A53,[1]Лист1!$A:$B,2,0)</f>
         <v>450 кг (акция сентябрь)</v>
       </c>
@@ -7490,7 +7625,7 @@
         <v>18.955467428778423</v>
       </c>
       <c r="AD53" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.216839609031615</v>
       </c>
       <c r="AE53" s="1">
@@ -7528,7 +7663,10 @@
         <f t="shared" si="13"/>
         <v>259</v>
       </c>
-      <c r="AP53" s="1"/>
+      <c r="AP53" s="1">
+        <f t="shared" si="14"/>
+        <v>94.964200000000005</v>
+      </c>
       <c r="AQ53" s="1"/>
       <c r="AR53" s="1"/>
       <c r="AS53" s="1"/>
@@ -7557,11 +7695,11 @@
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
       <c r="L54" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N54" s="11"/>
@@ -7575,7 +7713,7 @@
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
       <c r="V54" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="W54" s="13"/>
@@ -7588,14 +7726,14 @@
         <v>0</v>
       </c>
       <c r="Z54" s="5"/>
-      <c r="AA54" s="20"/>
-      <c r="AB54" s="19"/>
+      <c r="AA54" s="11"/>
+      <c r="AB54" s="1"/>
       <c r="AC54" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD54" s="11" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE54" s="11">
@@ -7633,7 +7771,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP54" s="1"/>
+      <c r="AP54" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ54" s="1"/>
       <c r="AR54" s="1"/>
       <c r="AS54" s="1"/>
@@ -7674,11 +7815,11 @@
         <v>347</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-7</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>340</v>
       </c>
       <c r="N55" s="1"/>
@@ -7692,7 +7833,7 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>68</v>
       </c>
       <c r="W55" s="5"/>
@@ -7705,14 +7846,14 @@
         <v>0</v>
       </c>
       <c r="Z55" s="5"/>
-      <c r="AA55" s="19"/>
-      <c r="AB55" s="19"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
       <c r="AC55" s="1">
         <f t="shared" si="11"/>
         <v>11.455882352941176</v>
       </c>
       <c r="AD55" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.455882352941176</v>
       </c>
       <c r="AE55" s="1">
@@ -7748,7 +7889,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP55" s="1"/>
+      <c r="AP55" s="1">
+        <f t="shared" si="14"/>
+        <v>30.6</v>
+      </c>
       <c r="AQ55" s="1"/>
       <c r="AR55" s="1"/>
       <c r="AS55" s="1"/>
@@ -7789,11 +7933,11 @@
         <v>436</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-9</v>
       </c>
       <c r="M56" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>427</v>
       </c>
       <c r="N56" s="1"/>
@@ -7809,7 +7953,7 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>85.4</v>
       </c>
       <c r="W56" s="5"/>
@@ -7822,14 +7966,14 @@
         <v>0</v>
       </c>
       <c r="Z56" s="5"/>
-      <c r="AA56" s="19"/>
-      <c r="AB56" s="19"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
       <c r="AC56" s="1">
         <f t="shared" si="11"/>
         <v>12.866951053864165</v>
       </c>
       <c r="AD56" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12.866951053864165</v>
       </c>
       <c r="AE56" s="1">
@@ -7865,7 +8009,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP56" s="1"/>
+      <c r="AP56" s="1">
+        <f t="shared" si="14"/>
+        <v>38.430000000000007</v>
+      </c>
       <c r="AQ56" s="1"/>
       <c r="AR56" s="1"/>
       <c r="AS56" s="1"/>
@@ -7894,11 +8041,11 @@
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
       <c r="L57" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M57" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N57" s="11"/>
@@ -7912,7 +8059,7 @@
       <c r="T57" s="11"/>
       <c r="U57" s="11"/>
       <c r="V57" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="W57" s="13"/>
@@ -7925,14 +8072,14 @@
         <v>0</v>
       </c>
       <c r="Z57" s="5"/>
-      <c r="AA57" s="20"/>
-      <c r="AB57" s="19"/>
+      <c r="AA57" s="11"/>
+      <c r="AB57" s="1"/>
       <c r="AC57" s="1" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD57" s="11" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE57" s="11">
@@ -7970,7 +8117,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP57" s="1"/>
+      <c r="AP57" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AQ57" s="1"/>
       <c r="AR57" s="1"/>
       <c r="AS57" s="1"/>
@@ -8011,11 +8161,11 @@
         <v>52</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-22</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="N58" s="1"/>
@@ -8031,7 +8181,7 @@
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
       <c r="W58" s="5"/>
@@ -8044,14 +8194,14 @@
         <v>0</v>
       </c>
       <c r="Z58" s="5"/>
-      <c r="AA58" s="19"/>
-      <c r="AB58" s="19"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
       <c r="AC58" s="1">
         <f t="shared" si="11"/>
         <v>17.666666666666668</v>
       </c>
       <c r="AD58" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>17.666666666666668</v>
       </c>
       <c r="AE58" s="1">
@@ -8089,7 +8239,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP58" s="1"/>
+      <c r="AP58" s="1">
+        <f t="shared" si="14"/>
+        <v>2.4000000000000004</v>
+      </c>
       <c r="AQ58" s="1"/>
       <c r="AR58" s="1"/>
       <c r="AS58" s="1"/>
@@ -8130,11 +8283,11 @@
         <v>664.57399999999996</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17.242000000000075</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>681.81600000000003</v>
       </c>
       <c r="N59" s="1"/>
@@ -8150,11 +8303,11 @@
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>136.36320000000001</v>
       </c>
       <c r="W59" s="5">
-        <f t="shared" ref="W59:W61" si="26">11*V59-U59-T59-S59-R59-Q59-P59-O59-F59</f>
+        <f t="shared" ref="W59:W61" si="27">11*V59-U59-T59-S59-R59-Q59-P59-O59-F59</f>
         <v>330.7803224000001</v>
       </c>
       <c r="X59" s="5">
@@ -8169,14 +8322,14 @@
         <f>X59*$Z$1</f>
         <v>190.13252931552006</v>
       </c>
-      <c r="AA59" s="19"/>
-      <c r="AB59" s="19"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
       <c r="AC59" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD59" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.5742698733969274</v>
       </c>
       <c r="AE59" s="1">
@@ -8212,7 +8365,10 @@
         <f t="shared" si="13"/>
         <v>190</v>
       </c>
-      <c r="AP59" s="1"/>
+      <c r="AP59" s="1">
+        <f t="shared" si="14"/>
+        <v>136.36320000000001</v>
+      </c>
       <c r="AQ59" s="1"/>
       <c r="AR59" s="1"/>
       <c r="AS59" s="1"/>
@@ -8255,11 +8411,11 @@
         <v>127</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>40</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>167</v>
       </c>
       <c r="N60" s="1"/>
@@ -8275,7 +8431,7 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>33.4</v>
       </c>
       <c r="W60" s="5"/>
@@ -8288,10 +8444,10 @@
         <v>50</v>
       </c>
       <c r="Z60" s="5"/>
-      <c r="AA60" s="19">
+      <c r="AA60" s="1">
         <v>50</v>
       </c>
-      <c r="AB60" s="19" t="s">
+      <c r="AB60" s="1" t="s">
         <v>202</v>
       </c>
       <c r="AC60" s="1">
@@ -8299,7 +8455,7 @@
         <v>36.67664670658683</v>
       </c>
       <c r="AD60" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>35.179640718562872</v>
       </c>
       <c r="AE60" s="1">
@@ -8335,7 +8491,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP60" s="1"/>
+      <c r="AP60" s="1">
+        <f t="shared" si="14"/>
+        <v>3.34</v>
+      </c>
       <c r="AQ60" s="1"/>
       <c r="AR60" s="1"/>
       <c r="AS60" s="1"/>
@@ -8376,11 +8535,11 @@
         <v>699.33199999999999</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-4.6770000000000209</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>490.12299999999993</v>
       </c>
       <c r="N61" s="1">
@@ -8396,11 +8555,11 @@
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>98.024599999999992</v>
       </c>
       <c r="W61" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>358.84629999999999</v>
       </c>
       <c r="X61" s="5">
@@ -8415,14 +8574,14 @@
         <f>X61*$Z$1</f>
         <v>206.26485323999998</v>
       </c>
-      <c r="AA61" s="19"/>
-      <c r="AB61" s="19"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
       <c r="AC61" s="1">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="AD61" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.3392219912144494</v>
       </c>
       <c r="AE61" s="1">
@@ -8458,7 +8617,10 @@
         <f t="shared" si="13"/>
         <v>206</v>
       </c>
-      <c r="AP61" s="1"/>
+      <c r="AP61" s="1">
+        <f t="shared" si="14"/>
+        <v>98.024599999999992</v>
+      </c>
       <c r="AQ61" s="1"/>
       <c r="AR61" s="1"/>
       <c r="AS61" s="1"/>
@@ -8499,11 +8661,11 @@
         <v>94.11</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-5.367999999999995</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>88.742000000000004</v>
       </c>
       <c r="N62" s="1"/>
@@ -8517,7 +8679,7 @@
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>17.7484</v>
       </c>
       <c r="W62" s="5">
@@ -8533,14 +8695,14 @@
         <v>109.2462</v>
       </c>
       <c r="Z62" s="5"/>
-      <c r="AA62" s="19"/>
-      <c r="AB62" s="19"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
       <c r="AC62" s="1">
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="AD62" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.8447296657726893</v>
       </c>
       <c r="AE62" s="1">
@@ -8576,7 +8738,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP62" s="1"/>
+      <c r="AP62" s="1">
+        <f t="shared" si="14"/>
+        <v>17.7484</v>
+      </c>
       <c r="AQ62" s="1"/>
       <c r="AR62" s="1"/>
       <c r="AS62" s="1"/>
@@ -8617,11 +8782,11 @@
         <v>146</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-17</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>129</v>
       </c>
       <c r="N63" s="1"/>
@@ -8637,7 +8802,7 @@
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>25.8</v>
       </c>
       <c r="W63" s="5"/>
@@ -8650,10 +8815,10 @@
         <v>50</v>
       </c>
       <c r="Z63" s="5"/>
-      <c r="AA63" s="19">
+      <c r="AA63" s="1">
         <v>50</v>
       </c>
-      <c r="AB63" s="19" t="str">
+      <c r="AB63" s="1" t="str">
         <f>VLOOKUP(A63,[1]Лист1!$A:$B,2,0)</f>
         <v>50 шт (акция сентябрь)</v>
       </c>
@@ -8662,7 +8827,7 @@
         <v>32.798449612403104</v>
       </c>
       <c r="AD63" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>30.86046511627907</v>
       </c>
       <c r="AE63" s="1">
@@ -8698,7 +8863,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP63" s="1"/>
+      <c r="AP63" s="1">
+        <f t="shared" si="14"/>
+        <v>2.58</v>
+      </c>
       <c r="AQ63" s="1"/>
       <c r="AR63" s="1"/>
       <c r="AS63" s="1"/>
@@ -8737,11 +8905,11 @@
         <v>17</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-14</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="N64" s="1"/>
@@ -8755,7 +8923,7 @@
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.6</v>
       </c>
       <c r="W64" s="5"/>
@@ -8768,14 +8936,14 @@
         <v>0</v>
       </c>
       <c r="Z64" s="5"/>
-      <c r="AA64" s="19"/>
-      <c r="AB64" s="19"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
       <c r="AC64" s="1">
         <f t="shared" si="11"/>
         <v>36.666666666666671</v>
       </c>
       <c r="AD64" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36.666666666666671</v>
       </c>
       <c r="AE64" s="1">
@@ -8813,7 +8981,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP64" s="1"/>
+      <c r="AP64" s="1">
+        <f t="shared" si="14"/>
+        <v>0.24</v>
+      </c>
       <c r="AQ64" s="1"/>
       <c r="AR64" s="1"/>
       <c r="AS64" s="1"/>
@@ -8854,11 +9025,11 @@
         <v>354.93</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-108.28200000000001</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>119.018</v>
       </c>
       <c r="N65" s="1">
@@ -8876,7 +9047,7 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23.803599999999999</v>
       </c>
       <c r="W65" s="5"/>
@@ -8889,10 +9060,10 @@
         <v>200</v>
       </c>
       <c r="Z65" s="5"/>
-      <c r="AA65" s="19">
+      <c r="AA65" s="1">
         <v>200</v>
       </c>
-      <c r="AB65" s="19" t="str">
+      <c r="AB65" s="1" t="str">
         <f>VLOOKUP(A65,[1]Лист1!$A:$B,2,0)</f>
         <v>200 кг (акция сентябрь)</v>
       </c>
@@ -8901,7 +9072,7 @@
         <v>39.483321850476401</v>
       </c>
       <c r="AD65" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>31.081231410374901</v>
       </c>
       <c r="AE65" s="1">
@@ -8939,7 +9110,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP65" s="1"/>
+      <c r="AP65" s="1">
+        <f t="shared" si="14"/>
+        <v>23.803599999999999</v>
+      </c>
       <c r="AQ65" s="1"/>
       <c r="AR65" s="1"/>
       <c r="AS65" s="1"/>
@@ -8980,11 +9154,11 @@
         <v>230.2</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-134.636</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>95.563999999999993</v>
       </c>
       <c r="N66" s="1"/>
@@ -9002,7 +9176,7 @@
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.1128</v>
       </c>
       <c r="W66" s="5">
@@ -9017,14 +9191,14 @@
         <v>100</v>
       </c>
       <c r="Z66" s="5"/>
-      <c r="AA66" s="19"/>
-      <c r="AB66" s="19"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
       <c r="AC66" s="1">
         <f t="shared" si="11"/>
         <v>20.123958812942114</v>
       </c>
       <c r="AD66" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.891863044661173</v>
       </c>
       <c r="AE66" s="1">
@@ -9062,7 +9236,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP66" s="1"/>
+      <c r="AP66" s="1">
+        <f t="shared" si="14"/>
+        <v>19.1128</v>
+      </c>
       <c r="AQ66" s="1"/>
       <c r="AR66" s="1"/>
       <c r="AS66" s="1"/>
@@ -9103,11 +9280,11 @@
         <v>547</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-73</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>474</v>
       </c>
       <c r="N67" s="1"/>
@@ -9123,7 +9300,7 @@
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>94.8</v>
       </c>
       <c r="W67" s="5">
@@ -9138,14 +9315,14 @@
         <v>150</v>
       </c>
       <c r="Z67" s="5"/>
-      <c r="AA67" s="19"/>
-      <c r="AB67" s="19"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
       <c r="AC67" s="1">
         <f t="shared" si="11"/>
         <v>24.229957805907173</v>
       </c>
       <c r="AD67" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.647679324894515</v>
       </c>
       <c r="AE67" s="1">
@@ -9181,7 +9358,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP67" s="1"/>
+      <c r="AP67" s="1">
+        <f t="shared" si="14"/>
+        <v>37.92</v>
+      </c>
       <c r="AQ67" s="1"/>
       <c r="AR67" s="1"/>
       <c r="AS67" s="1"/>
@@ -9222,11 +9402,11 @@
         <v>499</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-367</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>132</v>
       </c>
       <c r="N68" s="1"/>
@@ -9242,7 +9422,7 @@
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>26.4</v>
       </c>
       <c r="W68" s="5">
@@ -9260,14 +9440,14 @@
         <f>X68*$Z$1</f>
         <v>143.69999999999999</v>
       </c>
-      <c r="AA68" s="19"/>
-      <c r="AB68" s="19"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
       <c r="AC68" s="1">
         <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="AD68" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25.530303030303031</v>
       </c>
       <c r="AE68" s="1">
@@ -9303,7 +9483,10 @@
         <f t="shared" si="13"/>
         <v>57</v>
       </c>
-      <c r="AP68" s="1"/>
+      <c r="AP68" s="1">
+        <f t="shared" si="14"/>
+        <v>10.56</v>
+      </c>
       <c r="AQ68" s="1"/>
       <c r="AR68" s="1"/>
       <c r="AS68" s="1"/>
@@ -9344,11 +9527,11 @@
         <v>81.099999999999994</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-15.631</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>65.468999999999994</v>
       </c>
       <c r="N69" s="1"/>
@@ -9364,7 +9547,7 @@
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.093799999999998</v>
       </c>
       <c r="W69" s="5">
@@ -9379,10 +9562,10 @@
         <v>200</v>
       </c>
       <c r="Z69" s="5"/>
-      <c r="AA69" s="19">
+      <c r="AA69" s="1">
         <v>200</v>
       </c>
-      <c r="AB69" s="19" t="str">
+      <c r="AB69" s="1" t="str">
         <f>VLOOKUP(A69,[1]Лист1!$A:$B,2,0)</f>
         <v>200 кг (актуальный остаток ноль)</v>
       </c>
@@ -9391,7 +9574,7 @@
         <v>18.212665536360724</v>
       </c>
       <c r="AD69" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.9382608562831267</v>
       </c>
       <c r="AE69" s="1">
@@ -9427,7 +9610,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP69" s="1"/>
+      <c r="AP69" s="1">
+        <f t="shared" si="14"/>
+        <v>13.093799999999998</v>
+      </c>
       <c r="AQ69" s="1"/>
       <c r="AR69" s="1"/>
       <c r="AS69" s="1"/>
@@ -9468,11 +9654,11 @@
         <v>74.400000000000006</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="27">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="28">E70-K70</f>
         <v>-21.034000000000006</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M101" si="28">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="29">E70-N70</f>
         <v>53.366</v>
       </c>
       <c r="N70" s="1"/>
@@ -9492,7 +9678,7 @@
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V101" si="29">M70/5</f>
+        <f t="shared" ref="V70:V101" si="30">M70/5</f>
         <v>10.6732</v>
       </c>
       <c r="W70" s="5">
@@ -9507,14 +9693,14 @@
         <v>100</v>
       </c>
       <c r="Z70" s="5"/>
-      <c r="AA70" s="19"/>
-      <c r="AB70" s="19"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
       <c r="AC70" s="1">
         <f t="shared" si="11"/>
         <v>19.127688978000975</v>
       </c>
       <c r="AD70" s="1">
-        <f t="shared" ref="AD70:AD101" si="30">(F70+O70+P70+Q70+R70+S70+T70+U70)/V70</f>
+        <f t="shared" ref="AD70:AD101" si="31">(F70+O70+P70+Q70+R70+S70+T70+U70)/V70</f>
         <v>9.7584276505640304</v>
       </c>
       <c r="AE70" s="1">
@@ -9550,7 +9736,10 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP70" s="1"/>
+      <c r="AP70" s="1">
+        <f t="shared" si="14"/>
+        <v>10.6732</v>
+      </c>
       <c r="AQ70" s="1"/>
       <c r="AR70" s="1"/>
       <c r="AS70" s="1"/>
@@ -9591,11 +9780,11 @@
         <v>500.61</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-446.48</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>54.13</v>
       </c>
       <c r="N71" s="1"/>
@@ -9613,32 +9802,32 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>10.826000000000001</v>
       </c>
       <c r="W71" s="5">
         <v>250</v>
       </c>
       <c r="X71" s="5">
-        <f t="shared" ref="X71:X134" si="31">W71</f>
+        <f t="shared" ref="X71:X134" si="32">W71</f>
         <v>250</v>
       </c>
       <c r="Y71" s="5">
-        <f t="shared" ref="Y71:Y134" si="32">X71-Z71</f>
+        <f t="shared" ref="Y71:Y134" si="33">X71-Z71</f>
         <v>106.30000000000001</v>
       </c>
       <c r="Z71" s="5">
         <f>X71*$Z$1</f>
         <v>143.69999999999999</v>
       </c>
-      <c r="AA71" s="19"/>
-      <c r="AB71" s="19"/>
+      <c r="AA71" s="1"/>
+      <c r="AB71" s="1"/>
       <c r="AC71" s="1">
-        <f t="shared" ref="AC71:AC134" si="33">(F71+O71+P71+Q71+R71+S71+T71+U71+X71)/V71</f>
+        <f t="shared" ref="AC71:AC134" si="34">(F71+O71+P71+Q71+R71+S71+T71+U71+X71)/V71</f>
         <v>107.69129872529096</v>
       </c>
       <c r="AD71" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>84.598743765010155</v>
       </c>
       <c r="AE71" s="1">
@@ -9669,14 +9858,17 @@
         <v>42</v>
       </c>
       <c r="AN71" s="1">
-        <f t="shared" ref="AN71:AN134" si="34">ROUND(G71*Y71,0)</f>
+        <f t="shared" ref="AN71:AN134" si="35">ROUND(G71*Y71,0)</f>
         <v>106</v>
       </c>
       <c r="AO71" s="1">
-        <f t="shared" ref="AO71:AO134" si="35">ROUND(G71*Z71,0)</f>
+        <f t="shared" ref="AO71:AO134" si="36">ROUND(G71*Z71,0)</f>
         <v>144</v>
       </c>
-      <c r="AP71" s="1"/>
+      <c r="AP71" s="1">
+        <f t="shared" ref="AP71:AP134" si="37">V71*G71</f>
+        <v>10.826000000000001</v>
+      </c>
       <c r="AQ71" s="1"/>
       <c r="AR71" s="1"/>
       <c r="AS71" s="1"/>
@@ -9717,11 +9909,11 @@
         <v>22.503</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-0.62900000000000134</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>21.873999999999999</v>
       </c>
       <c r="N72" s="1"/>
@@ -9739,7 +9931,7 @@
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4.3747999999999996</v>
       </c>
       <c r="W72" s="5">
@@ -9750,23 +9942,23 @@
         <v>100</v>
       </c>
       <c r="Y72" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>100</v>
       </c>
       <c r="Z72" s="5"/>
-      <c r="AA72" s="19">
+      <c r="AA72" s="1">
         <v>100</v>
       </c>
-      <c r="AB72" s="19" t="str">
+      <c r="AB72" s="1" t="str">
         <f>VLOOKUP(A72,[1]Лист1!$A:$B,2,0)</f>
         <v>100 кг (остаток ноль)</v>
       </c>
       <c r="AC72" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21.319831763737774</v>
       </c>
       <c r="AD72" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.5383560391332169</v>
       </c>
       <c r="AE72" s="1">
@@ -9795,14 +9987,17 @@
       </c>
       <c r="AM72" s="1"/>
       <c r="AN72" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>100</v>
       </c>
       <c r="AO72" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP72" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP72" s="1">
+        <f t="shared" si="37"/>
+        <v>4.3747999999999996</v>
+      </c>
       <c r="AQ72" s="1"/>
       <c r="AR72" s="1"/>
       <c r="AS72" s="1"/>
@@ -9831,11 +10026,11 @@
       <c r="J73" s="11"/>
       <c r="K73" s="11"/>
       <c r="L73" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M73" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N73" s="11"/>
@@ -9849,27 +10044,27 @@
       <c r="T73" s="11"/>
       <c r="U73" s="11"/>
       <c r="V73" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W73" s="13"/>
       <c r="X73" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y73" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="5"/>
+      <c r="AA73" s="11"/>
+      <c r="AB73" s="1"/>
+      <c r="AC73" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD73" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y73" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z73" s="5"/>
-      <c r="AA73" s="20"/>
-      <c r="AB73" s="19"/>
-      <c r="AC73" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD73" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE73" s="11">
@@ -9900,14 +10095,17 @@
         <v>63</v>
       </c>
       <c r="AN73" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO73" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP73" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP73" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ73" s="1"/>
       <c r="AR73" s="1"/>
       <c r="AS73" s="1"/>
@@ -9948,11 +10146,11 @@
         <v>214.5</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-30.216000000000008</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>184.28399999999999</v>
       </c>
       <c r="N74" s="1"/>
@@ -9968,7 +10166,7 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>36.8568</v>
       </c>
       <c r="W74" s="5">
@@ -9976,22 +10174,22 @@
         <v>57.487799999999993</v>
       </c>
       <c r="X74" s="5">
-        <f t="shared" si="31"/>
-        <v>57.487799999999993</v>
-      </c>
-      <c r="Y74" s="5">
         <f t="shared" si="32"/>
         <v>57.487799999999993</v>
       </c>
+      <c r="Y74" s="5">
+        <f t="shared" si="33"/>
+        <v>57.487799999999993</v>
+      </c>
       <c r="Z74" s="5"/>
-      <c r="AA74" s="19"/>
-      <c r="AB74" s="19"/>
+      <c r="AA74" s="1"/>
+      <c r="AB74" s="1"/>
       <c r="AC74" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD74" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.4402389789672458</v>
       </c>
       <c r="AE74" s="1">
@@ -10022,14 +10220,17 @@
         <v>125</v>
       </c>
       <c r="AN74" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>57</v>
       </c>
       <c r="AO74" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP74" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP74" s="1">
+        <f t="shared" si="37"/>
+        <v>36.8568</v>
+      </c>
       <c r="AQ74" s="1"/>
       <c r="AR74" s="1"/>
       <c r="AS74" s="1"/>
@@ -10062,11 +10263,11 @@
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
       <c r="L75" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M75" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N75" s="11"/>
@@ -10080,27 +10281,27 @@
       <c r="T75" s="11"/>
       <c r="U75" s="11"/>
       <c r="V75" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W75" s="13"/>
       <c r="X75" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y75" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z75" s="5"/>
+      <c r="AA75" s="11"/>
+      <c r="AB75" s="1"/>
+      <c r="AC75" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD75" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y75" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z75" s="5"/>
-      <c r="AA75" s="20"/>
-      <c r="AB75" s="19"/>
-      <c r="AC75" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD75" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE75" s="11">
@@ -10129,14 +10330,17 @@
       </c>
       <c r="AM75" s="11"/>
       <c r="AN75" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO75" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP75" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP75" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ75" s="1"/>
       <c r="AR75" s="1"/>
       <c r="AS75" s="1"/>
@@ -10177,11 +10381,11 @@
         <v>1557</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-244</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1313</v>
       </c>
       <c r="N76" s="1"/>
@@ -10195,27 +10399,27 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>262.60000000000002</v>
       </c>
       <c r="W76" s="5"/>
       <c r="X76" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z76" s="5"/>
+      <c r="AA76" s="1"/>
+      <c r="AB76" s="1"/>
+      <c r="AC76" s="1">
+        <f t="shared" si="34"/>
+        <v>12.602437166793601</v>
+      </c>
+      <c r="AD76" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y76" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z76" s="5"/>
-      <c r="AA76" s="19"/>
-      <c r="AB76" s="19"/>
-      <c r="AC76" s="1">
-        <f t="shared" si="33"/>
-        <v>12.602437166793601</v>
-      </c>
-      <c r="AD76" s="1">
-        <f t="shared" si="30"/>
         <v>12.602437166793601</v>
       </c>
       <c r="AE76" s="1">
@@ -10244,14 +10448,17 @@
       </c>
       <c r="AM76" s="1"/>
       <c r="AN76" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO76" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP76" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP76" s="1">
+        <f t="shared" si="37"/>
+        <v>157.56</v>
+      </c>
       <c r="AQ76" s="1"/>
       <c r="AR76" s="1"/>
       <c r="AS76" s="1"/>
@@ -10292,11 +10499,11 @@
         <v>596</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-12</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>584</v>
       </c>
       <c r="N77" s="1"/>
@@ -10310,27 +10517,27 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>116.8</v>
       </c>
       <c r="W77" s="5"/>
       <c r="X77" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="5"/>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
+      <c r="AC77" s="1">
+        <f t="shared" si="34"/>
+        <v>14.211415525114157</v>
+      </c>
+      <c r="AD77" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y77" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z77" s="5"/>
-      <c r="AA77" s="19"/>
-      <c r="AB77" s="19"/>
-      <c r="AC77" s="1">
-        <f t="shared" si="33"/>
-        <v>14.211415525114157</v>
-      </c>
-      <c r="AD77" s="1">
-        <f t="shared" si="30"/>
         <v>14.211415525114157</v>
       </c>
       <c r="AE77" s="1">
@@ -10359,14 +10566,17 @@
       </c>
       <c r="AM77" s="1"/>
       <c r="AN77" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO77" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP77" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP77" s="1">
+        <f t="shared" si="37"/>
+        <v>70.08</v>
+      </c>
       <c r="AQ77" s="1"/>
       <c r="AR77" s="1"/>
       <c r="AS77" s="1"/>
@@ -10405,11 +10615,11 @@
         <v>31</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-6</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>25</v>
       </c>
       <c r="N78" s="1"/>
@@ -10423,27 +10633,27 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>5</v>
       </c>
       <c r="W78" s="5"/>
       <c r="X78" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y78" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="5"/>
+      <c r="AA78" s="1"/>
+      <c r="AB78" s="1"/>
+      <c r="AC78" s="1">
+        <f t="shared" si="34"/>
+        <v>13</v>
+      </c>
+      <c r="AD78" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y78" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z78" s="5"/>
-      <c r="AA78" s="19"/>
-      <c r="AB78" s="19"/>
-      <c r="AC78" s="1">
-        <f t="shared" si="33"/>
-        <v>13</v>
-      </c>
-      <c r="AD78" s="1">
-        <f t="shared" si="30"/>
         <v>13</v>
       </c>
       <c r="AE78" s="1">
@@ -10474,14 +10684,17 @@
         <v>130</v>
       </c>
       <c r="AN78" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO78" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP78" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP78" s="1">
+        <f t="shared" si="37"/>
+        <v>2</v>
+      </c>
       <c r="AQ78" s="1"/>
       <c r="AR78" s="1"/>
       <c r="AS78" s="1"/>
@@ -10516,11 +10729,11 @@
         <v>2</v>
       </c>
       <c r="L79" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="M79" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N79" s="11"/>
@@ -10534,27 +10747,27 @@
       <c r="T79" s="11"/>
       <c r="U79" s="11"/>
       <c r="V79" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W79" s="13"/>
       <c r="X79" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y79" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z79" s="5"/>
+      <c r="AA79" s="11"/>
+      <c r="AB79" s="1"/>
+      <c r="AC79" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD79" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y79" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z79" s="5"/>
-      <c r="AA79" s="20"/>
-      <c r="AB79" s="19"/>
-      <c r="AC79" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD79" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE79" s="11">
@@ -10585,14 +10798,17 @@
         <v>63</v>
       </c>
       <c r="AN79" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO79" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP79" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP79" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ79" s="1"/>
       <c r="AR79" s="1"/>
       <c r="AS79" s="1"/>
@@ -10631,11 +10847,11 @@
         <v>55</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-12</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>43</v>
       </c>
       <c r="N80" s="1"/>
@@ -10651,29 +10867,29 @@
       </c>
       <c r="U80" s="1"/>
       <c r="V80" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.6</v>
       </c>
       <c r="W80" s="5">
         <v>40</v>
       </c>
       <c r="X80" s="5">
-        <f t="shared" si="31"/>
-        <v>40</v>
-      </c>
-      <c r="Y80" s="5">
         <f t="shared" si="32"/>
         <v>40</v>
       </c>
+      <c r="Y80" s="5">
+        <f t="shared" si="33"/>
+        <v>40</v>
+      </c>
       <c r="Z80" s="5"/>
-      <c r="AA80" s="19"/>
-      <c r="AB80" s="19"/>
+      <c r="AA80" s="1"/>
+      <c r="AB80" s="1"/>
       <c r="AC80" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.1162790697674421</v>
       </c>
       <c r="AD80" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.4651162790697676</v>
       </c>
       <c r="AE80" s="1">
@@ -10702,14 +10918,17 @@
       </c>
       <c r="AM80" s="1"/>
       <c r="AN80" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>14</v>
       </c>
       <c r="AO80" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP80" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP80" s="1">
+        <f t="shared" si="37"/>
+        <v>3.01</v>
+      </c>
       <c r="AQ80" s="1"/>
       <c r="AR80" s="1"/>
       <c r="AS80" s="1"/>
@@ -10750,11 +10969,11 @@
         <v>123</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-4</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>119</v>
       </c>
       <c r="N81" s="1"/>
@@ -10768,27 +10987,27 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>23.8</v>
       </c>
       <c r="W81" s="5"/>
       <c r="X81" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y81" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="5"/>
+      <c r="AA81" s="1"/>
+      <c r="AB81" s="1"/>
+      <c r="AC81" s="1">
+        <f t="shared" si="34"/>
+        <v>13.61344537815126</v>
+      </c>
+      <c r="AD81" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y81" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="5"/>
-      <c r="AA81" s="19"/>
-      <c r="AB81" s="19"/>
-      <c r="AC81" s="1">
-        <f t="shared" si="33"/>
-        <v>13.61344537815126</v>
-      </c>
-      <c r="AD81" s="1">
-        <f t="shared" si="30"/>
         <v>13.61344537815126</v>
       </c>
       <c r="AE81" s="1">
@@ -10817,14 +11036,17 @@
       </c>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO81" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP81" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP81" s="1">
+        <f t="shared" si="37"/>
+        <v>8.8060000000000009</v>
+      </c>
       <c r="AQ81" s="1"/>
       <c r="AR81" s="1"/>
       <c r="AS81" s="1"/>
@@ -10865,11 +11087,11 @@
         <v>227</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>226</v>
       </c>
       <c r="N82" s="1"/>
@@ -10883,27 +11105,27 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>45.2</v>
       </c>
       <c r="W82" s="5"/>
       <c r="X82" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y82" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z82" s="5"/>
+      <c r="AA82" s="1"/>
+      <c r="AB82" s="1"/>
+      <c r="AC82" s="1">
+        <f t="shared" si="34"/>
+        <v>11.013716814159292</v>
+      </c>
+      <c r="AD82" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y82" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z82" s="5"/>
-      <c r="AA82" s="19"/>
-      <c r="AB82" s="19"/>
-      <c r="AC82" s="1">
-        <f t="shared" si="33"/>
-        <v>11.013716814159292</v>
-      </c>
-      <c r="AD82" s="1">
-        <f t="shared" si="30"/>
         <v>11.013716814159292</v>
       </c>
       <c r="AE82" s="1">
@@ -10932,14 +11154,17 @@
       </c>
       <c r="AM82" s="1"/>
       <c r="AN82" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO82" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP82" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP82" s="1">
+        <f t="shared" si="37"/>
+        <v>27.12</v>
+      </c>
       <c r="AQ82" s="1"/>
       <c r="AR82" s="1"/>
       <c r="AS82" s="1"/>
@@ -10980,11 +11205,11 @@
         <v>416</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-23</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>393</v>
       </c>
       <c r="N83" s="1"/>
@@ -10998,33 +11223,33 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>78.599999999999994</v>
       </c>
       <c r="W83" s="5">
-        <f t="shared" ref="W83" si="36">11*V83-U83-T83-S83-R83-Q83-P83-O83-F83</f>
+        <f t="shared" ref="W83" si="38">11*V83-U83-T83-S83-R83-Q83-P83-O83-F83</f>
         <v>253.59999999999991</v>
       </c>
       <c r="X83" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>253.59999999999991</v>
       </c>
       <c r="Y83" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>107.83071999999996</v>
       </c>
       <c r="Z83" s="5">
         <f>X83*$Z$1</f>
         <v>145.76927999999995</v>
       </c>
-      <c r="AA83" s="19"/>
-      <c r="AB83" s="19"/>
+      <c r="AA83" s="1"/>
+      <c r="AB83" s="1"/>
       <c r="AC83" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD83" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.773536895674301</v>
       </c>
       <c r="AE83" s="1">
@@ -11053,14 +11278,17 @@
       </c>
       <c r="AM83" s="1"/>
       <c r="AN83" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="AO83" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>48</v>
       </c>
-      <c r="AP83" s="1"/>
+      <c r="AP83" s="1">
+        <f t="shared" si="37"/>
+        <v>25.937999999999999</v>
+      </c>
       <c r="AQ83" s="1"/>
       <c r="AR83" s="1"/>
       <c r="AS83" s="1"/>
@@ -11101,11 +11329,11 @@
         <v>47</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-9</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>38</v>
       </c>
       <c r="N84" s="1"/>
@@ -11119,27 +11347,27 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.6</v>
       </c>
       <c r="W84" s="5"/>
       <c r="X84" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z84" s="5"/>
+      <c r="AA84" s="1"/>
+      <c r="AB84" s="1"/>
+      <c r="AC84" s="1">
+        <f t="shared" si="34"/>
+        <v>14.210526315789476</v>
+      </c>
+      <c r="AD84" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y84" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z84" s="5"/>
-      <c r="AA84" s="19"/>
-      <c r="AB84" s="19"/>
-      <c r="AC84" s="1">
-        <f t="shared" si="33"/>
-        <v>14.210526315789476</v>
-      </c>
-      <c r="AD84" s="1">
-        <f t="shared" si="30"/>
         <v>14.210526315789476</v>
       </c>
       <c r="AE84" s="1">
@@ -11168,14 +11396,17 @@
       </c>
       <c r="AM84" s="1"/>
       <c r="AN84" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO84" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP84" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP84" s="1">
+        <f t="shared" si="37"/>
+        <v>3.04</v>
+      </c>
       <c r="AQ84" s="1"/>
       <c r="AR84" s="1"/>
       <c r="AS84" s="1"/>
@@ -11216,11 +11447,11 @@
         <v>22</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-25</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="N85" s="1"/>
@@ -11238,29 +11469,29 @@
       </c>
       <c r="U85" s="1"/>
       <c r="V85" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-0.6</v>
       </c>
       <c r="W85" s="5">
         <v>100</v>
       </c>
       <c r="X85" s="5">
-        <f t="shared" si="31"/>
-        <v>100</v>
-      </c>
-      <c r="Y85" s="5">
         <f t="shared" si="32"/>
         <v>100</v>
       </c>
+      <c r="Y85" s="5">
+        <f t="shared" si="33"/>
+        <v>100</v>
+      </c>
       <c r="Z85" s="5"/>
-      <c r="AA85" s="19"/>
-      <c r="AB85" s="19"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
       <c r="AC85" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-351.66666666666669</v>
       </c>
       <c r="AD85" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-185</v>
       </c>
       <c r="AE85" s="1">
@@ -11289,14 +11520,17 @@
       </c>
       <c r="AM85" s="1"/>
       <c r="AN85" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>35</v>
       </c>
       <c r="AO85" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP85" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP85" s="1">
+        <f t="shared" si="37"/>
+        <v>-0.21</v>
+      </c>
       <c r="AQ85" s="1"/>
       <c r="AR85" s="1"/>
       <c r="AS85" s="1"/>
@@ -11337,11 +11571,11 @@
         <v>68</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-62</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>6</v>
       </c>
       <c r="N86" s="1"/>
@@ -11357,27 +11591,27 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.2</v>
       </c>
       <c r="W86" s="5"/>
       <c r="X86" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y86" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z86" s="5"/>
+      <c r="AA86" s="1"/>
+      <c r="AB86" s="1"/>
+      <c r="AC86" s="1">
+        <f t="shared" si="34"/>
+        <v>369.16666666666669</v>
+      </c>
+      <c r="AD86" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y86" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z86" s="5"/>
-      <c r="AA86" s="19"/>
-      <c r="AB86" s="19"/>
-      <c r="AC86" s="1">
-        <f t="shared" si="33"/>
-        <v>369.16666666666669</v>
-      </c>
-      <c r="AD86" s="1">
-        <f t="shared" si="30"/>
         <v>369.16666666666669</v>
       </c>
       <c r="AE86" s="1">
@@ -11406,14 +11640,17 @@
       </c>
       <c r="AM86" s="1"/>
       <c r="AN86" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO86" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP86" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP86" s="1">
+        <f t="shared" si="37"/>
+        <v>0.42</v>
+      </c>
       <c r="AQ86" s="1"/>
       <c r="AR86" s="1"/>
       <c r="AS86" s="1"/>
@@ -11452,11 +11689,11 @@
         <v>31</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>31</v>
       </c>
       <c r="N87" s="1"/>
@@ -11470,7 +11707,7 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.2</v>
       </c>
       <c r="W87" s="5">
@@ -11478,22 +11715,22 @@
         <v>12</v>
       </c>
       <c r="X87" s="5">
-        <f t="shared" si="31"/>
-        <v>12</v>
-      </c>
-      <c r="Y87" s="5">
         <f t="shared" si="32"/>
         <v>12</v>
       </c>
+      <c r="Y87" s="5">
+        <f t="shared" si="33"/>
+        <v>12</v>
+      </c>
       <c r="Z87" s="5"/>
-      <c r="AA87" s="19"/>
-      <c r="AB87" s="19"/>
+      <c r="AA87" s="1"/>
+      <c r="AB87" s="1"/>
       <c r="AC87" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="AD87" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.064516129032258</v>
       </c>
       <c r="AE87" s="1">
@@ -11522,14 +11759,17 @@
       </c>
       <c r="AM87" s="1"/>
       <c r="AN87" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5</v>
       </c>
       <c r="AO87" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP87" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP87" s="1">
+        <f t="shared" si="37"/>
+        <v>2.4800000000000004</v>
+      </c>
       <c r="AQ87" s="1"/>
       <c r="AR87" s="1"/>
       <c r="AS87" s="1"/>
@@ -11568,11 +11808,11 @@
         <v>1.3</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3.499999999999992E-2</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.335</v>
       </c>
       <c r="N88" s="1"/>
@@ -11586,27 +11826,27 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.26700000000000002</v>
       </c>
       <c r="W88" s="5"/>
       <c r="X88" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y88" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z88" s="5"/>
+      <c r="AA88" s="1"/>
+      <c r="AB88" s="1"/>
+      <c r="AC88" s="1">
+        <f t="shared" si="34"/>
+        <v>78.543071161048687</v>
+      </c>
+      <c r="AD88" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y88" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z88" s="5"/>
-      <c r="AA88" s="19"/>
-      <c r="AB88" s="19"/>
-      <c r="AC88" s="1">
-        <f t="shared" si="33"/>
-        <v>78.543071161048687</v>
-      </c>
-      <c r="AD88" s="1">
-        <f t="shared" si="30"/>
         <v>78.543071161048687</v>
       </c>
       <c r="AE88" s="1">
@@ -11637,14 +11877,17 @@
         <v>112</v>
       </c>
       <c r="AN88" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO88" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP88" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP88" s="1">
+        <f t="shared" si="37"/>
+        <v>0.26700000000000002</v>
+      </c>
       <c r="AQ88" s="1"/>
       <c r="AR88" s="1"/>
       <c r="AS88" s="1"/>
@@ -11673,11 +11916,11 @@
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
       <c r="L89" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M89" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N89" s="11"/>
@@ -11691,27 +11934,27 @@
       <c r="T89" s="11"/>
       <c r="U89" s="11"/>
       <c r="V89" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W89" s="13"/>
       <c r="X89" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y89" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z89" s="5"/>
+      <c r="AA89" s="11"/>
+      <c r="AB89" s="1"/>
+      <c r="AC89" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD89" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y89" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z89" s="5"/>
-      <c r="AA89" s="20"/>
-      <c r="AB89" s="19"/>
-      <c r="AC89" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD89" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE89" s="11">
@@ -11742,14 +11985,17 @@
         <v>63</v>
       </c>
       <c r="AN89" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO89" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP89" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP89" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ89" s="1"/>
       <c r="AR89" s="1"/>
       <c r="AS89" s="1"/>
@@ -11790,11 +12036,11 @@
         <v>2994.2069999999999</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-4.6999999999998181</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2693.6750000000002</v>
       </c>
       <c r="N90" s="1">
@@ -11812,33 +12058,33 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>538.73500000000001</v>
       </c>
       <c r="W90" s="5">
-        <f t="shared" ref="W90:W95" si="37">11*V90-U90-T90-S90-R90-Q90-P90-O90-F90</f>
+        <f t="shared" ref="W90:W95" si="39">11*V90-U90-T90-S90-R90-Q90-P90-O90-F90</f>
         <v>820.55089999999973</v>
       </c>
       <c r="X90" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>820.55089999999973</v>
       </c>
       <c r="Y90" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>348.8982426799999</v>
       </c>
       <c r="Z90" s="5">
         <f>X90*$Z$1</f>
         <v>471.65265731999983</v>
       </c>
-      <c r="AA90" s="19"/>
-      <c r="AB90" s="19"/>
+      <c r="AA90" s="1"/>
+      <c r="AB90" s="1"/>
       <c r="AC90" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AD90" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.4768932777710742</v>
       </c>
       <c r="AE90" s="1">
@@ -11869,14 +12115,17 @@
         <v>42</v>
       </c>
       <c r="AN90" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>349</v>
       </c>
       <c r="AO90" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>472</v>
       </c>
-      <c r="AP90" s="1"/>
+      <c r="AP90" s="1">
+        <f t="shared" si="37"/>
+        <v>538.73500000000001</v>
+      </c>
       <c r="AQ90" s="1"/>
       <c r="AR90" s="1"/>
       <c r="AS90" s="1"/>
@@ -11917,11 +12166,11 @@
         <v>370</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-46</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>324</v>
       </c>
       <c r="N91" s="1"/>
@@ -11935,27 +12184,27 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>64.8</v>
       </c>
       <c r="W91" s="5"/>
       <c r="X91" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z91" s="5"/>
+      <c r="AA91" s="1"/>
+      <c r="AB91" s="1"/>
+      <c r="AC91" s="1">
+        <f t="shared" si="34"/>
+        <v>12.067901234567902</v>
+      </c>
+      <c r="AD91" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y91" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z91" s="5"/>
-      <c r="AA91" s="19"/>
-      <c r="AB91" s="19"/>
-      <c r="AC91" s="1">
-        <f t="shared" si="33"/>
-        <v>12.067901234567902</v>
-      </c>
-      <c r="AD91" s="1">
-        <f t="shared" si="30"/>
         <v>12.067901234567902</v>
       </c>
       <c r="AE91" s="1">
@@ -11984,14 +12233,17 @@
       </c>
       <c r="AM91" s="1"/>
       <c r="AN91" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO91" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP91" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP91" s="1">
+        <f t="shared" si="37"/>
+        <v>19.439999999999998</v>
+      </c>
       <c r="AQ91" s="1"/>
       <c r="AR91" s="1"/>
       <c r="AS91" s="1"/>
@@ -12032,11 +12284,11 @@
         <v>1594.9169999999999</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-57.113999999999805</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1387.3760000000002</v>
       </c>
       <c r="N92" s="1">
@@ -12054,37 +12306,37 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>277.47520000000003</v>
       </c>
       <c r="W92" s="5">
-        <f t="shared" ref="W92:W94" si="38">10*V92-U92-T92-S92-R92-Q92-P92-O92-F92</f>
+        <f t="shared" ref="W92:W94" si="40">10*V92-U92-T92-S92-R92-Q92-P92-O92-F92</f>
         <v>475.20519999999988</v>
       </c>
       <c r="X92" s="5">
         <v>700</v>
       </c>
       <c r="Y92" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>297.64000000000004</v>
       </c>
       <c r="Z92" s="5">
-        <f t="shared" ref="Z92:Z94" si="39">X92*$Z$1</f>
+        <f t="shared" ref="Z92:Z94" si="41">X92*$Z$1</f>
         <v>402.35999999999996</v>
       </c>
-      <c r="AA92" s="19">
+      <c r="AA92" s="1">
         <v>1000</v>
       </c>
-      <c r="AB92" s="19" t="str">
+      <c r="AB92" s="1" t="str">
         <f>VLOOKUP(A92,[1]Лист1!$A:$B,2,0)</f>
         <v>1000 кг (акция сентябрь)</v>
       </c>
       <c r="AC92" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.81014375338769</v>
       </c>
       <c r="AD92" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.2873957744692142</v>
       </c>
       <c r="AE92" s="1">
@@ -12113,14 +12365,17 @@
       </c>
       <c r="AM92" s="1"/>
       <c r="AN92" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>298</v>
       </c>
       <c r="AO92" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>402</v>
       </c>
-      <c r="AP92" s="1"/>
+      <c r="AP92" s="1">
+        <f t="shared" si="37"/>
+        <v>277.47520000000003</v>
+      </c>
       <c r="AQ92" s="1"/>
       <c r="AR92" s="1"/>
       <c r="AS92" s="1"/>
@@ -12161,11 +12416,11 @@
         <v>3941.2539999999999</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-85.23700000000008</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2478.4609999999998</v>
       </c>
       <c r="N93" s="1">
@@ -12183,37 +12438,37 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>495.69219999999996</v>
       </c>
       <c r="W93" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1344.6770000000001</v>
       </c>
       <c r="X93" s="5">
         <v>1800</v>
       </c>
       <c r="Y93" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>765.36000000000013</v>
       </c>
       <c r="Z93" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1034.6399999999999</v>
       </c>
-      <c r="AA93" s="19">
+      <c r="AA93" s="1">
         <v>2500</v>
       </c>
-      <c r="AB93" s="19" t="str">
+      <c r="AB93" s="1" t="str">
         <f>VLOOKUP(A93,[1]Лист1!$A:$B,2,0)</f>
         <v>2500 кг (акция сентябрь)</v>
       </c>
       <c r="AC93" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.918559945062681</v>
       </c>
       <c r="AD93" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.2872742399416408</v>
       </c>
       <c r="AE93" s="1">
@@ -12242,14 +12497,17 @@
       </c>
       <c r="AM93" s="1"/>
       <c r="AN93" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>765</v>
       </c>
       <c r="AO93" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1035</v>
       </c>
-      <c r="AP93" s="1"/>
+      <c r="AP93" s="1">
+        <f t="shared" si="37"/>
+        <v>495.69219999999996</v>
+      </c>
       <c r="AQ93" s="1"/>
       <c r="AR93" s="1"/>
       <c r="AS93" s="1"/>
@@ -12291,11 +12549,11 @@
         <v>4288.8029999999999</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-115.15300000000025</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2946.5819999999994</v>
       </c>
       <c r="N94" s="1">
@@ -12313,37 +12571,37 @@
         <v>600</v>
       </c>
       <c r="V94" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>589.31639999999993</v>
       </c>
       <c r="W94" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1319.6889999999989</v>
       </c>
       <c r="X94" s="5">
         <v>1800</v>
       </c>
       <c r="Y94" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>765.36000000000013</v>
       </c>
       <c r="Z94" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1034.6399999999999</v>
       </c>
-      <c r="AA94" s="19">
+      <c r="AA94" s="1">
         <v>2500</v>
       </c>
-      <c r="AB94" s="19" t="str">
+      <c r="AB94" s="1" t="str">
         <f>VLOOKUP(A94,[1]Лист1!$A:$B,2,0)</f>
         <v>2500 кг (акция сентябрь)</v>
       </c>
       <c r="AC94" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.815030771246144</v>
       </c>
       <c r="AD94" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.7606443669309062</v>
       </c>
       <c r="AE94" s="1">
@@ -12372,14 +12630,17 @@
       </c>
       <c r="AM94" s="1"/>
       <c r="AN94" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>765</v>
       </c>
       <c r="AO94" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1035</v>
       </c>
-      <c r="AP94" s="1"/>
+      <c r="AP94" s="1">
+        <f t="shared" si="37"/>
+        <v>589.31639999999993</v>
+      </c>
       <c r="AQ94" s="1"/>
       <c r="AR94" s="1"/>
       <c r="AS94" s="1"/>
@@ -12418,11 +12679,11 @@
         <v>20.55</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-0.30700000000000216</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>20.242999999999999</v>
       </c>
       <c r="N95" s="1"/>
@@ -12436,30 +12697,30 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4.0485999999999995</v>
       </c>
       <c r="W95" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>13.0763</v>
       </c>
       <c r="X95" s="5">
-        <f t="shared" si="31"/>
-        <v>13.0763</v>
-      </c>
-      <c r="Y95" s="5">
         <f t="shared" si="32"/>
         <v>13.0763</v>
       </c>
+      <c r="Y95" s="5">
+        <f t="shared" si="33"/>
+        <v>13.0763</v>
+      </c>
       <c r="Z95" s="5"/>
-      <c r="AA95" s="19"/>
-      <c r="AB95" s="19"/>
+      <c r="AA95" s="1"/>
+      <c r="AB95" s="1"/>
       <c r="AC95" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD95" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.7701674652966464</v>
       </c>
       <c r="AE95" s="1">
@@ -12488,14 +12749,17 @@
       </c>
       <c r="AM95" s="1"/>
       <c r="AN95" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>13</v>
       </c>
       <c r="AO95" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP95" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP95" s="1">
+        <f t="shared" si="37"/>
+        <v>4.0485999999999995</v>
+      </c>
       <c r="AQ95" s="1"/>
       <c r="AR95" s="1"/>
       <c r="AS95" s="1"/>
@@ -12528,11 +12792,11 @@
       <c r="J96" s="11"/>
       <c r="K96" s="11"/>
       <c r="L96" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M96" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N96" s="11"/>
@@ -12546,27 +12810,27 @@
       <c r="T96" s="11"/>
       <c r="U96" s="11"/>
       <c r="V96" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W96" s="13"/>
       <c r="X96" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y96" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z96" s="5"/>
+      <c r="AA96" s="11"/>
+      <c r="AB96" s="1"/>
+      <c r="AC96" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD96" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y96" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z96" s="5"/>
-      <c r="AA96" s="20"/>
-      <c r="AB96" s="19"/>
-      <c r="AC96" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD96" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE96" s="11">
@@ -12595,14 +12859,17 @@
       </c>
       <c r="AM96" s="11"/>
       <c r="AN96" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO96" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP96" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP96" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ96" s="1"/>
       <c r="AR96" s="1"/>
       <c r="AS96" s="1"/>
@@ -12637,11 +12904,11 @@
         <v>5</v>
       </c>
       <c r="L97" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-5</v>
       </c>
       <c r="M97" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N97" s="11"/>
@@ -12655,27 +12922,27 @@
       <c r="T97" s="11"/>
       <c r="U97" s="11"/>
       <c r="V97" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W97" s="13"/>
       <c r="X97" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y97" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z97" s="5"/>
+      <c r="AA97" s="11"/>
+      <c r="AB97" s="1"/>
+      <c r="AC97" s="1" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD97" s="11" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y97" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z97" s="5"/>
-      <c r="AA97" s="20"/>
-      <c r="AB97" s="19"/>
-      <c r="AC97" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD97" s="11" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE97" s="11">
@@ -12704,14 +12971,17 @@
       </c>
       <c r="AM97" s="11"/>
       <c r="AN97" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO97" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP97" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP97" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ97" s="1"/>
       <c r="AR97" s="1"/>
       <c r="AS97" s="1"/>
@@ -12750,11 +13020,11 @@
         <v>87</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-89</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-2</v>
       </c>
       <c r="N98" s="1"/>
@@ -12770,7 +13040,7 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-0.4</v>
       </c>
       <c r="W98" s="5">
@@ -12781,23 +13051,23 @@
         <v>100</v>
       </c>
       <c r="Y98" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>100</v>
       </c>
       <c r="Z98" s="5"/>
-      <c r="AA98" s="19">
+      <c r="AA98" s="1">
         <v>100</v>
       </c>
-      <c r="AB98" s="19" t="str">
+      <c r="AB98" s="1" t="str">
         <f>VLOOKUP(A98,[1]Лист1!$A:$B,2,0)</f>
         <v>100 шт</v>
       </c>
       <c r="AC98" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-412.5</v>
       </c>
       <c r="AD98" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-162.5</v>
       </c>
       <c r="AE98" s="1">
@@ -12826,14 +13096,17 @@
       </c>
       <c r="AM98" s="1"/>
       <c r="AN98" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AO98" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP98" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP98" s="1">
+        <f t="shared" si="37"/>
+        <v>-0.12</v>
+      </c>
       <c r="AQ98" s="1"/>
       <c r="AR98" s="1"/>
       <c r="AS98" s="1"/>
@@ -12874,11 +13147,11 @@
         <v>41</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-9</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>32</v>
       </c>
       <c r="N99" s="1"/>
@@ -12892,27 +13165,27 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.4</v>
       </c>
       <c r="W99" s="5"/>
       <c r="X99" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y99" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z99" s="5"/>
+      <c r="AA99" s="1"/>
+      <c r="AB99" s="1"/>
+      <c r="AC99" s="1">
+        <f t="shared" si="34"/>
+        <v>11.9375</v>
+      </c>
+      <c r="AD99" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y99" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z99" s="5"/>
-      <c r="AA99" s="19"/>
-      <c r="AB99" s="19"/>
-      <c r="AC99" s="1">
-        <f t="shared" si="33"/>
-        <v>11.9375</v>
-      </c>
-      <c r="AD99" s="1">
-        <f t="shared" si="30"/>
         <v>11.9375</v>
       </c>
       <c r="AE99" s="1">
@@ -12941,14 +13214,17 @@
       </c>
       <c r="AM99" s="1"/>
       <c r="AN99" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO99" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP99" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP99" s="1">
+        <f t="shared" si="37"/>
+        <v>1.92</v>
+      </c>
       <c r="AQ99" s="1"/>
       <c r="AR99" s="1"/>
       <c r="AS99" s="1"/>
@@ -12989,11 +13265,11 @@
         <v>285</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-283</v>
       </c>
       <c r="M100" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="N100" s="1"/>
@@ -13009,27 +13285,27 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.4</v>
       </c>
       <c r="W100" s="5"/>
       <c r="X100" s="5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y100" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Z100" s="5"/>
+      <c r="AA100" s="1"/>
+      <c r="AB100" s="1"/>
+      <c r="AC100" s="1">
+        <f t="shared" si="34"/>
+        <v>280</v>
+      </c>
+      <c r="AD100" s="1">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="Y100" s="5">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Z100" s="5"/>
-      <c r="AA100" s="19"/>
-      <c r="AB100" s="19"/>
-      <c r="AC100" s="1">
-        <f t="shared" si="33"/>
-        <v>280</v>
-      </c>
-      <c r="AD100" s="1">
-        <f t="shared" si="30"/>
         <v>280</v>
       </c>
       <c r="AE100" s="1">
@@ -13060,14 +13336,17 @@
         <v>112</v>
       </c>
       <c r="AN100" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO100" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP100" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP100" s="1">
+        <f t="shared" si="37"/>
+        <v>2.8000000000000004E-2</v>
+      </c>
       <c r="AQ100" s="1"/>
       <c r="AR100" s="1"/>
       <c r="AS100" s="1"/>
@@ -13108,11 +13387,11 @@
         <v>243</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-72</v>
       </c>
       <c r="M101" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>171</v>
       </c>
       <c r="N101" s="1"/>
@@ -13130,30 +13409,30 @@
       </c>
       <c r="U101" s="1"/>
       <c r="V101" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>34.200000000000003</v>
       </c>
       <c r="W101" s="5">
-        <f t="shared" ref="W101" si="40">11*V101-U101-T101-S101-R101-Q101-P101-O101-F101</f>
+        <f t="shared" ref="W101" si="42">11*V101-U101-T101-S101-R101-Q101-P101-O101-F101</f>
         <v>154.30000000000007</v>
       </c>
       <c r="X101" s="5">
-        <f t="shared" si="31"/>
-        <v>154.30000000000007</v>
-      </c>
-      <c r="Y101" s="5">
         <f t="shared" si="32"/>
         <v>154.30000000000007</v>
       </c>
+      <c r="Y101" s="5">
+        <f t="shared" si="33"/>
+        <v>154.30000000000007</v>
+      </c>
       <c r="Z101" s="5"/>
-      <c r="AA101" s="19"/>
-      <c r="AB101" s="19"/>
+      <c r="AA101" s="1"/>
+      <c r="AB101" s="1"/>
       <c r="AC101" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD101" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.4883040935672502</v>
       </c>
       <c r="AE101" s="1">
@@ -13184,14 +13463,17 @@
         <v>155</v>
       </c>
       <c r="AN101" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AO101" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP101" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP101" s="1">
+        <f t="shared" si="37"/>
+        <v>2.3940000000000006</v>
+      </c>
       <c r="AQ101" s="1"/>
       <c r="AR101" s="1"/>
       <c r="AS101" s="1"/>
@@ -13232,11 +13514,11 @@
         <v>120</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="41">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="43">E102-K102</f>
         <v>-63</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" ref="M102:M133" si="42">E102-N102</f>
+        <f t="shared" ref="M102:M133" si="44">E102-N102</f>
         <v>57</v>
       </c>
       <c r="N102" s="1"/>
@@ -13254,29 +13536,29 @@
       </c>
       <c r="U102" s="1"/>
       <c r="V102" s="1">
-        <f t="shared" ref="V102:V138" si="43">M102/5</f>
+        <f t="shared" ref="V102:V138" si="45">M102/5</f>
         <v>11.4</v>
       </c>
       <c r="W102" s="5">
         <v>50</v>
       </c>
       <c r="X102" s="5">
-        <f t="shared" si="31"/>
-        <v>50</v>
-      </c>
-      <c r="Y102" s="5">
         <f t="shared" si="32"/>
         <v>50</v>
       </c>
+      <c r="Y102" s="5">
+        <f t="shared" si="33"/>
+        <v>50</v>
+      </c>
       <c r="Z102" s="5"/>
-      <c r="AA102" s="19"/>
-      <c r="AB102" s="19"/>
+      <c r="AA102" s="1"/>
+      <c r="AB102" s="1"/>
       <c r="AC102" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>22.631578947368421</v>
       </c>
       <c r="AD102" s="1">
-        <f t="shared" ref="AD102:AD138" si="44">(F102+O102+P102+Q102+R102+S102+T102+U102)/V102</f>
+        <f t="shared" ref="AD102:AD138" si="46">(F102+O102+P102+Q102+R102+S102+T102+U102)/V102</f>
         <v>18.245614035087719</v>
       </c>
       <c r="AE102" s="1">
@@ -13307,14 +13589,17 @@
         <v>153</v>
       </c>
       <c r="AN102" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4</v>
       </c>
       <c r="AO102" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP102" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP102" s="1">
+        <f t="shared" si="37"/>
+        <v>0.79800000000000015</v>
+      </c>
       <c r="AQ102" s="1"/>
       <c r="AR102" s="1"/>
       <c r="AS102" s="1"/>
@@ -13353,11 +13638,11 @@
         <v>95</v>
       </c>
       <c r="L103" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-97</v>
       </c>
       <c r="M103" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>-2</v>
       </c>
       <c r="N103" s="11"/>
@@ -13371,27 +13656,27 @@
       <c r="T103" s="11"/>
       <c r="U103" s="11"/>
       <c r="V103" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.4</v>
       </c>
       <c r="W103" s="13"/>
       <c r="X103" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y103" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z103" s="5"/>
-      <c r="AA103" s="20"/>
-      <c r="AB103" s="19"/>
+      <c r="AA103" s="11"/>
+      <c r="AB103" s="1"/>
       <c r="AC103" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-10</v>
       </c>
       <c r="AD103" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-10</v>
       </c>
       <c r="AE103" s="11">
@@ -13420,14 +13705,17 @@
       </c>
       <c r="AM103" s="11"/>
       <c r="AN103" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO103" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP103" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP103" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ103" s="1"/>
       <c r="AR103" s="1"/>
       <c r="AS103" s="1"/>
@@ -13468,11 +13756,11 @@
         <v>46</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-26</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>20</v>
       </c>
       <c r="N104" s="1"/>
@@ -13486,27 +13774,27 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>4</v>
       </c>
       <c r="W104" s="5"/>
       <c r="X104" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y104" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z104" s="5"/>
-      <c r="AA104" s="19"/>
-      <c r="AB104" s="19"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
       <c r="AC104" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13</v>
       </c>
       <c r="AD104" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>13</v>
       </c>
       <c r="AE104" s="1">
@@ -13535,14 +13823,17 @@
       </c>
       <c r="AM104" s="1"/>
       <c r="AN104" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO104" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP104" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP104" s="1">
+        <f t="shared" si="37"/>
+        <v>1.2</v>
+      </c>
       <c r="AQ104" s="1"/>
       <c r="AR104" s="1"/>
       <c r="AS104" s="1"/>
@@ -13583,11 +13874,11 @@
         <v>16.8</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.5990000000000002</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>16.201000000000001</v>
       </c>
       <c r="N105" s="1"/>
@@ -13603,29 +13894,29 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>3.2402000000000002</v>
       </c>
       <c r="W105" s="5">
         <v>5</v>
       </c>
       <c r="X105" s="5">
-        <f t="shared" si="31"/>
-        <v>5</v>
-      </c>
-      <c r="Y105" s="5">
         <f t="shared" si="32"/>
         <v>5</v>
       </c>
+      <c r="Y105" s="5">
+        <f t="shared" si="33"/>
+        <v>5</v>
+      </c>
       <c r="Z105" s="5"/>
-      <c r="AA105" s="19"/>
-      <c r="AB105" s="19"/>
+      <c r="AA105" s="1"/>
+      <c r="AB105" s="1"/>
       <c r="AC105" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.496389111783225</v>
       </c>
       <c r="AD105" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.9532744892290612</v>
       </c>
       <c r="AE105" s="1">
@@ -13654,14 +13945,17 @@
       </c>
       <c r="AM105" s="1"/>
       <c r="AN105" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5</v>
       </c>
       <c r="AO105" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP105" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP105" s="1">
+        <f t="shared" si="37"/>
+        <v>3.2402000000000002</v>
+      </c>
       <c r="AQ105" s="1"/>
       <c r="AR105" s="1"/>
       <c r="AS105" s="1"/>
@@ -13702,11 +13996,11 @@
         <v>299</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-243</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>56</v>
       </c>
       <c r="N106" s="1"/>
@@ -13720,27 +14014,27 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>11.2</v>
       </c>
       <c r="W106" s="5"/>
       <c r="X106" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y106" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z106" s="5"/>
-      <c r="AA106" s="19"/>
-      <c r="AB106" s="19"/>
+      <c r="AA106" s="1"/>
+      <c r="AB106" s="1"/>
       <c r="AC106" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>45.535714285714292</v>
       </c>
       <c r="AD106" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>45.535714285714292</v>
       </c>
       <c r="AE106" s="1">
@@ -13771,14 +14065,17 @@
         <v>197</v>
       </c>
       <c r="AN106" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO106" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP106" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP106" s="1">
+        <f t="shared" si="37"/>
+        <v>1.232</v>
+      </c>
       <c r="AQ106" s="1"/>
       <c r="AR106" s="1"/>
       <c r="AS106" s="1"/>
@@ -13807,11 +14104,11 @@
       <c r="J107" s="11"/>
       <c r="K107" s="11"/>
       <c r="L107" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M107" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N107" s="11"/>
@@ -13825,27 +14122,27 @@
       <c r="T107" s="11"/>
       <c r="U107" s="11"/>
       <c r="V107" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="W107" s="13"/>
       <c r="X107" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y107" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z107" s="5"/>
-      <c r="AA107" s="20"/>
-      <c r="AB107" s="19"/>
+      <c r="AA107" s="11"/>
+      <c r="AB107" s="1"/>
       <c r="AC107" s="1" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD107" s="11" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE107" s="11">
@@ -13876,14 +14173,17 @@
         <v>63</v>
       </c>
       <c r="AN107" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO107" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP107" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP107" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ107" s="1"/>
       <c r="AR107" s="1"/>
       <c r="AS107" s="1"/>
@@ -13924,11 +14224,11 @@
         <v>475</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-83</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>392</v>
       </c>
       <c r="N108" s="1"/>
@@ -13942,27 +14242,27 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>78.400000000000006</v>
       </c>
       <c r="W108" s="5"/>
       <c r="X108" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y108" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z108" s="5"/>
-      <c r="AA108" s="19"/>
-      <c r="AB108" s="19"/>
+      <c r="AA108" s="1"/>
+      <c r="AB108" s="1"/>
       <c r="AC108" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.656887755102039</v>
       </c>
       <c r="AD108" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>11.656887755102039</v>
       </c>
       <c r="AE108" s="1">
@@ -13993,14 +14293,17 @@
         <v>163</v>
       </c>
       <c r="AN108" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO108" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP108" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP108" s="1">
+        <f t="shared" si="37"/>
+        <v>6.2720000000000002</v>
+      </c>
       <c r="AQ108" s="1"/>
       <c r="AR108" s="1"/>
       <c r="AS108" s="1"/>
@@ -14041,11 +14344,11 @@
         <v>373</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-71</v>
       </c>
       <c r="M109" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>302</v>
       </c>
       <c r="N109" s="1"/>
@@ -14061,27 +14364,27 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>60.4</v>
       </c>
       <c r="W109" s="5"/>
       <c r="X109" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y109" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z109" s="5"/>
-      <c r="AA109" s="19"/>
-      <c r="AB109" s="19"/>
+      <c r="AA109" s="1"/>
+      <c r="AB109" s="1"/>
       <c r="AC109" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15.139218543046356</v>
       </c>
       <c r="AD109" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>15.139218543046356</v>
       </c>
       <c r="AE109" s="1">
@@ -14112,14 +14415,17 @@
         <v>165</v>
       </c>
       <c r="AN109" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO109" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP109" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP109" s="1">
+        <f t="shared" si="37"/>
+        <v>4.8319999999999999</v>
+      </c>
       <c r="AQ109" s="1"/>
       <c r="AR109" s="1"/>
       <c r="AS109" s="1"/>
@@ -14160,11 +14466,11 @@
         <v>261</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-204</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>57</v>
       </c>
       <c r="N110" s="1"/>
@@ -14178,27 +14484,27 @@
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>11.4</v>
       </c>
       <c r="W110" s="5"/>
       <c r="X110" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y110" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z110" s="5"/>
-      <c r="AA110" s="19"/>
-      <c r="AB110" s="19"/>
+      <c r="AA110" s="1"/>
+      <c r="AB110" s="1"/>
       <c r="AC110" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>40.350877192982452</v>
       </c>
       <c r="AD110" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>40.350877192982452</v>
       </c>
       <c r="AE110" s="1">
@@ -14229,14 +14535,17 @@
         <v>198</v>
       </c>
       <c r="AN110" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO110" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP110" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP110" s="1">
+        <f t="shared" si="37"/>
+        <v>1.9380000000000002</v>
+      </c>
       <c r="AQ110" s="1"/>
       <c r="AR110" s="1"/>
       <c r="AS110" s="1"/>
@@ -14277,11 +14586,11 @@
         <v>295.74</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-70.89700000000002</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>224.84299999999999</v>
       </c>
       <c r="N111" s="1"/>
@@ -14297,38 +14606,38 @@
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>44.968599999999995</v>
       </c>
       <c r="W111" s="5">
-        <f t="shared" ref="W111" si="45">11*V111-U111-T111-S111-R111-Q111-P111-O111-F111</f>
+        <f t="shared" ref="W111" si="47">11*V111-U111-T111-S111-R111-Q111-P111-O111-F111</f>
         <v>151.03259999999983</v>
       </c>
       <c r="X111" s="5">
-        <f t="shared" ref="X111:X112" si="46">AA111</f>
+        <f t="shared" ref="X111:X112" si="48">AA111</f>
         <v>250</v>
       </c>
       <c r="Y111" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>106.30000000000001</v>
       </c>
       <c r="Z111" s="5">
-        <f t="shared" ref="Z111:Z112" si="47">X111*$Z$1</f>
+        <f t="shared" ref="Z111:Z112" si="49">X111*$Z$1</f>
         <v>143.69999999999999</v>
       </c>
-      <c r="AA111" s="19">
+      <c r="AA111" s="1">
         <v>250</v>
       </c>
-      <c r="AB111" s="19" t="str">
+      <c r="AB111" s="1" t="str">
         <f>VLOOKUP(A111,[1]Лист1!$A:$B,2,0)</f>
         <v>250 кг (акция сентябрь)</v>
       </c>
       <c r="AC111" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13.200811232726839</v>
       </c>
       <c r="AD111" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>7.6413764271069171</v>
       </c>
       <c r="AE111" s="1">
@@ -14357,14 +14666,17 @@
       </c>
       <c r="AM111" s="1"/>
       <c r="AN111" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>106</v>
       </c>
       <c r="AO111" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>144</v>
       </c>
-      <c r="AP111" s="1"/>
+      <c r="AP111" s="1">
+        <f t="shared" si="37"/>
+        <v>44.968599999999995</v>
+      </c>
       <c r="AQ111" s="1"/>
       <c r="AR111" s="1"/>
       <c r="AS111" s="1"/>
@@ -14405,11 +14717,11 @@
         <v>294.07</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-66.756</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>227.31399999999999</v>
       </c>
       <c r="N112" s="1"/>
@@ -14425,37 +14737,37 @@
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>45.462800000000001</v>
       </c>
       <c r="W112" s="5">
         <v>300</v>
       </c>
       <c r="X112" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>450</v>
       </c>
       <c r="Y112" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>191.34000000000003</v>
       </c>
       <c r="Z112" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>258.65999999999997</v>
       </c>
-      <c r="AA112" s="19">
+      <c r="AA112" s="1">
         <v>450</v>
       </c>
-      <c r="AB112" s="19" t="str">
+      <c r="AB112" s="1" t="str">
         <f>VLOOKUP(A112,[1]Лист1!$A:$B,2,0)</f>
         <v>450 кг (акция сентябрь)</v>
       </c>
       <c r="AC112" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13.827700889518463</v>
       </c>
       <c r="AD112" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.9294984030899984</v>
       </c>
       <c r="AE112" s="1">
@@ -14484,14 +14796,17 @@
       </c>
       <c r="AM112" s="1"/>
       <c r="AN112" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>191</v>
       </c>
       <c r="AO112" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>259</v>
       </c>
-      <c r="AP112" s="1"/>
+      <c r="AP112" s="1">
+        <f t="shared" si="37"/>
+        <v>45.462800000000001</v>
+      </c>
       <c r="AQ112" s="1"/>
       <c r="AR112" s="1"/>
       <c r="AS112" s="1"/>
@@ -14530,11 +14845,11 @@
         <v>17.3</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-20.941000000000003</v>
       </c>
       <c r="M113" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>-3.641</v>
       </c>
       <c r="N113" s="1"/>
@@ -14552,29 +14867,29 @@
       </c>
       <c r="U113" s="1"/>
       <c r="V113" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.72819999999999996</v>
       </c>
       <c r="W113" s="5">
         <v>50</v>
       </c>
       <c r="X113" s="5">
-        <f t="shared" si="31"/>
-        <v>50</v>
-      </c>
-      <c r="Y113" s="5">
         <f t="shared" si="32"/>
         <v>50</v>
       </c>
+      <c r="Y113" s="5">
+        <f t="shared" si="33"/>
+        <v>50</v>
+      </c>
       <c r="Z113" s="5"/>
-      <c r="AA113" s="19"/>
-      <c r="AB113" s="19"/>
+      <c r="AA113" s="1"/>
+      <c r="AB113" s="1"/>
       <c r="AC113" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-87.745124965668779</v>
       </c>
       <c r="AD113" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-19.082669596264765</v>
       </c>
       <c r="AE113" s="1">
@@ -14603,14 +14918,17 @@
       </c>
       <c r="AM113" s="1"/>
       <c r="AN113" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>50</v>
       </c>
       <c r="AO113" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP113" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP113" s="1">
+        <f t="shared" si="37"/>
+        <v>-0.72819999999999996</v>
+      </c>
       <c r="AQ113" s="1"/>
       <c r="AR113" s="1"/>
       <c r="AS113" s="1"/>
@@ -14651,11 +14969,11 @@
         <v>80</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-69</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>11</v>
       </c>
       <c r="N114" s="1"/>
@@ -14669,27 +14987,27 @@
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="W114" s="5"/>
       <c r="X114" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y114" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z114" s="5"/>
-      <c r="AA114" s="19"/>
-      <c r="AB114" s="19"/>
+      <c r="AA114" s="1"/>
+      <c r="AB114" s="1"/>
       <c r="AC114" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>28.636363636363633</v>
       </c>
       <c r="AD114" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>28.636363636363633</v>
       </c>
       <c r="AE114" s="1">
@@ -14720,14 +15038,17 @@
         <v>140</v>
       </c>
       <c r="AN114" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO114" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP114" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP114" s="1">
+        <f t="shared" si="37"/>
+        <v>0.66</v>
+      </c>
       <c r="AQ114" s="1"/>
       <c r="AR114" s="1"/>
       <c r="AS114" s="1"/>
@@ -14768,11 +15089,11 @@
         <v>6.6</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-3.9019999999999997</v>
       </c>
       <c r="M115" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>2.698</v>
       </c>
       <c r="N115" s="1"/>
@@ -14786,27 +15107,27 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.53959999999999997</v>
       </c>
       <c r="W115" s="5"/>
       <c r="X115" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y115" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z115" s="5"/>
-      <c r="AA115" s="19"/>
-      <c r="AB115" s="19"/>
+      <c r="AA115" s="1"/>
+      <c r="AB115" s="1"/>
       <c r="AC115" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>28.47479614529281</v>
       </c>
       <c r="AD115" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>28.47479614529281</v>
       </c>
       <c r="AE115" s="1">
@@ -14837,14 +15158,17 @@
         <v>112</v>
       </c>
       <c r="AN115" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO115" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP115" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP115" s="1">
+        <f t="shared" si="37"/>
+        <v>0.53959999999999997</v>
+      </c>
       <c r="AQ115" s="1"/>
       <c r="AR115" s="1"/>
       <c r="AS115" s="1"/>
@@ -14885,11 +15209,11 @@
         <v>488</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-340</v>
       </c>
       <c r="M116" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>148</v>
       </c>
       <c r="N116" s="1"/>
@@ -14905,27 +15229,27 @@
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>29.6</v>
       </c>
       <c r="W116" s="5"/>
       <c r="X116" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y116" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z116" s="5"/>
-      <c r="AA116" s="19"/>
-      <c r="AB116" s="19"/>
+      <c r="AA116" s="1"/>
+      <c r="AB116" s="1"/>
       <c r="AC116" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>40.945945945945944</v>
       </c>
       <c r="AD116" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>40.945945945945944</v>
       </c>
       <c r="AE116" s="1">
@@ -14956,14 +15280,17 @@
         <v>140</v>
       </c>
       <c r="AN116" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO116" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP116" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP116" s="1">
+        <f t="shared" si="37"/>
+        <v>8.288000000000002</v>
+      </c>
       <c r="AQ116" s="1"/>
       <c r="AR116" s="1"/>
       <c r="AS116" s="1"/>
@@ -15004,11 +15331,11 @@
         <v>577</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-221</v>
       </c>
       <c r="M117" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>356</v>
       </c>
       <c r="N117" s="1"/>
@@ -15024,7 +15351,7 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>71.2</v>
       </c>
       <c r="W117" s="5">
@@ -15035,26 +15362,26 @@
         <v>600</v>
       </c>
       <c r="Y117" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>255.12</v>
       </c>
       <c r="Z117" s="5">
         <f>X117*$Z$1</f>
         <v>344.88</v>
       </c>
-      <c r="AA117" s="19">
+      <c r="AA117" s="1">
         <v>600</v>
       </c>
-      <c r="AB117" s="19" t="str">
+      <c r="AB117" s="1" t="str">
         <f>VLOOKUP(A117,[1]Лист1!$A:$B,2,0)</f>
         <v>600 шт</v>
       </c>
       <c r="AC117" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.6169382022471908</v>
       </c>
       <c r="AD117" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1.1899719101123596</v>
       </c>
       <c r="AE117" s="1">
@@ -15083,14 +15410,17 @@
       </c>
       <c r="AM117" s="1"/>
       <c r="AN117" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>71</v>
       </c>
       <c r="AO117" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>97</v>
       </c>
-      <c r="AP117" s="1"/>
+      <c r="AP117" s="1">
+        <f t="shared" si="37"/>
+        <v>19.936000000000003</v>
+      </c>
       <c r="AQ117" s="1"/>
       <c r="AR117" s="1"/>
       <c r="AS117" s="1"/>
@@ -15131,11 +15461,11 @@
         <v>536</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-209</v>
       </c>
       <c r="M118" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>327</v>
       </c>
       <c r="N118" s="1"/>
@@ -15151,27 +15481,27 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>65.400000000000006</v>
       </c>
       <c r="W118" s="5"/>
       <c r="X118" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y118" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z118" s="5"/>
-      <c r="AA118" s="19"/>
-      <c r="AB118" s="19"/>
+      <c r="AA118" s="1"/>
+      <c r="AB118" s="1"/>
       <c r="AC118" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20.61926605504587</v>
       </c>
       <c r="AD118" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>20.61926605504587</v>
       </c>
       <c r="AE118" s="1">
@@ -15200,14 +15530,17 @@
       </c>
       <c r="AM118" s="1"/>
       <c r="AN118" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO118" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP118" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP118" s="1">
+        <f t="shared" si="37"/>
+        <v>18.312000000000005</v>
+      </c>
       <c r="AQ118" s="1"/>
       <c r="AR118" s="1"/>
       <c r="AS118" s="1"/>
@@ -15248,11 +15581,11 @@
         <v>301</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-80</v>
       </c>
       <c r="M119" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>221</v>
       </c>
       <c r="N119" s="1"/>
@@ -15268,27 +15601,27 @@
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>44.2</v>
       </c>
       <c r="W119" s="5"/>
       <c r="X119" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y119" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z119" s="5"/>
-      <c r="AA119" s="19"/>
-      <c r="AB119" s="19"/>
+      <c r="AA119" s="1"/>
+      <c r="AB119" s="1"/>
       <c r="AC119" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>17.109764705882352</v>
       </c>
       <c r="AD119" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>17.109764705882352</v>
       </c>
       <c r="AE119" s="1">
@@ -15319,14 +15652,17 @@
         <v>176</v>
       </c>
       <c r="AN119" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO119" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP119" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP119" s="1">
+        <f t="shared" si="37"/>
+        <v>3.9780000000000002</v>
+      </c>
       <c r="AQ119" s="1"/>
       <c r="AR119" s="1"/>
       <c r="AS119" s="1"/>
@@ -15361,11 +15697,11 @@
       <c r="J120" s="11"/>
       <c r="K120" s="11"/>
       <c r="L120" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M120" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N120" s="11"/>
@@ -15379,27 +15715,27 @@
       <c r="T120" s="11"/>
       <c r="U120" s="11"/>
       <c r="V120" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="W120" s="13"/>
       <c r="X120" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y120" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z120" s="5"/>
-      <c r="AA120" s="20"/>
-      <c r="AB120" s="19"/>
+      <c r="AA120" s="11"/>
+      <c r="AB120" s="1"/>
       <c r="AC120" s="1" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD120" s="11" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE120" s="11">
@@ -15428,14 +15764,17 @@
       </c>
       <c r="AM120" s="11"/>
       <c r="AN120" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO120" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP120" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP120" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AQ120" s="1"/>
       <c r="AR120" s="1"/>
       <c r="AS120" s="1"/>
@@ -15476,11 +15815,11 @@
         <v>42.344000000000001</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-3.0750000000000028</v>
       </c>
       <c r="M121" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>39.268999999999998</v>
       </c>
       <c r="N121" s="1"/>
@@ -15494,30 +15833,30 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>7.8537999999999997</v>
       </c>
       <c r="W121" s="5">
-        <f t="shared" ref="W121:W134" si="48">11*V121-U121-T121-S121-R121-Q121-P121-O121-F121</f>
+        <f t="shared" ref="W121:W134" si="50">11*V121-U121-T121-S121-R121-Q121-P121-O121-F121</f>
         <v>42.582399999999993</v>
       </c>
       <c r="X121" s="5">
-        <f t="shared" si="31"/>
-        <v>42.582399999999993</v>
-      </c>
-      <c r="Y121" s="5">
         <f t="shared" si="32"/>
         <v>42.582399999999993</v>
       </c>
+      <c r="Y121" s="5">
+        <f t="shared" si="33"/>
+        <v>42.582399999999993</v>
+      </c>
       <c r="Z121" s="5"/>
-      <c r="AA121" s="19"/>
-      <c r="AB121" s="19"/>
+      <c r="AA121" s="1"/>
+      <c r="AB121" s="1"/>
       <c r="AC121" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AD121" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>5.5781150525860079</v>
       </c>
       <c r="AE121" s="1">
@@ -15546,14 +15885,17 @@
       </c>
       <c r="AM121" s="1"/>
       <c r="AN121" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>43</v>
       </c>
       <c r="AO121" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP121" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP121" s="1">
+        <f t="shared" si="37"/>
+        <v>7.8537999999999997</v>
+      </c>
       <c r="AQ121" s="1"/>
       <c r="AR121" s="1"/>
       <c r="AS121" s="1"/>
@@ -15592,11 +15934,11 @@
         <v>27.393999999999998</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.60999999999999943</v>
       </c>
       <c r="M122" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>26.783999999999999</v>
       </c>
       <c r="N122" s="1"/>
@@ -15610,7 +15952,7 @@
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>5.3567999999999998</v>
       </c>
       <c r="W122" s="5">
@@ -15618,22 +15960,22 @@
         <v>29.238999999999997</v>
       </c>
       <c r="X122" s="5">
-        <f t="shared" si="31"/>
-        <v>29.238999999999997</v>
-      </c>
-      <c r="Y122" s="5">
         <f t="shared" si="32"/>
         <v>29.238999999999997</v>
       </c>
+      <c r="Y122" s="5">
+        <f t="shared" si="33"/>
+        <v>29.238999999999997</v>
+      </c>
       <c r="Z122" s="5"/>
-      <c r="AA122" s="19"/>
-      <c r="AB122" s="19"/>
+      <c r="AA122" s="1"/>
+      <c r="AB122" s="1"/>
       <c r="AC122" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="AD122" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4.5417040023894861</v>
       </c>
       <c r="AE122" s="1">
@@ -15662,14 +16004,17 @@
       </c>
       <c r="AM122" s="1"/>
       <c r="AN122" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>29</v>
       </c>
       <c r="AO122" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP122" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP122" s="1">
+        <f t="shared" si="37"/>
+        <v>5.3567999999999998</v>
+      </c>
       <c r="AQ122" s="1"/>
       <c r="AR122" s="1"/>
       <c r="AS122" s="1"/>
@@ -15710,11 +16055,11 @@
         <v>144</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-58</v>
       </c>
       <c r="M123" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>86</v>
       </c>
       <c r="N123" s="1"/>
@@ -15730,27 +16075,27 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>17.2</v>
       </c>
       <c r="W123" s="5"/>
       <c r="X123" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y123" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z123" s="5"/>
-      <c r="AA123" s="19"/>
-      <c r="AB123" s="19"/>
+      <c r="AA123" s="1"/>
+      <c r="AB123" s="1"/>
       <c r="AC123" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>36.483569767441857</v>
       </c>
       <c r="AD123" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>36.483569767441857</v>
       </c>
       <c r="AE123" s="1">
@@ -15781,14 +16126,17 @@
         <v>153</v>
       </c>
       <c r="AN123" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO123" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP123" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP123" s="1">
+        <f t="shared" si="37"/>
+        <v>1.5479999999999998</v>
+      </c>
       <c r="AQ123" s="1"/>
       <c r="AR123" s="1"/>
       <c r="AS123" s="1"/>
@@ -15829,11 +16177,11 @@
         <v>178</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-39</v>
       </c>
       <c r="M124" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>139</v>
       </c>
       <c r="N124" s="1"/>
@@ -15849,27 +16197,27 @@
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>27.8</v>
       </c>
       <c r="W124" s="5"/>
       <c r="X124" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y124" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z124" s="5"/>
-      <c r="AA124" s="19"/>
-      <c r="AB124" s="19"/>
+      <c r="AA124" s="1"/>
+      <c r="AB124" s="1"/>
       <c r="AC124" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20.792697841726618</v>
       </c>
       <c r="AD124" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>20.792697841726618</v>
       </c>
       <c r="AE124" s="1">
@@ -15900,14 +16248,17 @@
         <v>155</v>
       </c>
       <c r="AN124" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO124" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP124" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP124" s="1">
+        <f t="shared" si="37"/>
+        <v>2.5019999999999998</v>
+      </c>
       <c r="AQ124" s="1"/>
       <c r="AR124" s="1"/>
       <c r="AS124" s="1"/>
@@ -15948,11 +16299,11 @@
         <v>118.759</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.53499999999999659</v>
       </c>
       <c r="M125" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>119.294</v>
       </c>
       <c r="N125" s="1"/>
@@ -15966,27 +16317,27 @@
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>23.858799999999999</v>
       </c>
       <c r="W125" s="5"/>
       <c r="X125" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y125" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z125" s="5"/>
-      <c r="AA125" s="19"/>
-      <c r="AB125" s="19"/>
+      <c r="AA125" s="1"/>
+      <c r="AB125" s="1"/>
       <c r="AC125" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>12.215253910506814</v>
       </c>
       <c r="AD125" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>12.215253910506814</v>
       </c>
       <c r="AE125" s="1">
@@ -16017,14 +16368,17 @@
         <v>42</v>
       </c>
       <c r="AN125" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO125" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP125" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP125" s="1">
+        <f t="shared" si="37"/>
+        <v>23.858799999999999</v>
+      </c>
       <c r="AQ125" s="1"/>
       <c r="AR125" s="1"/>
       <c r="AS125" s="1"/>
@@ -16065,11 +16419,11 @@
         <v>767.62800000000004</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.31899999999996</v>
       </c>
       <c r="M126" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>774.947</v>
       </c>
       <c r="N126" s="1"/>
@@ -16085,11 +16439,11 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>154.98939999999999</v>
       </c>
       <c r="W126" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>47.296599999999785</v>
       </c>
       <c r="X126" s="5">
@@ -16097,23 +16451,23 @@
         <v>200</v>
       </c>
       <c r="Y126" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>200</v>
       </c>
       <c r="Z126" s="5"/>
-      <c r="AA126" s="19">
+      <c r="AA126" s="1">
         <v>200</v>
       </c>
-      <c r="AB126" s="19" t="str">
+      <c r="AB126" s="1" t="str">
         <f>VLOOKUP(A126,[1]Лист1!$A:$B,2,0)</f>
         <v>200кг (акция сентябрь)</v>
       </c>
       <c r="AC126" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.985250604234873</v>
       </c>
       <c r="AD126" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>10.694839776139531</v>
       </c>
       <c r="AE126" s="1">
@@ -16144,14 +16498,17 @@
         <v>42</v>
       </c>
       <c r="AN126" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>200</v>
       </c>
       <c r="AO126" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP126" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP126" s="1">
+        <f t="shared" si="37"/>
+        <v>154.98939999999999</v>
+      </c>
       <c r="AQ126" s="1"/>
       <c r="AR126" s="1"/>
       <c r="AS126" s="1"/>
@@ -16192,11 +16549,11 @@
         <v>69.477000000000004</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.8539999999999992</v>
       </c>
       <c r="M127" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>68.623000000000005</v>
       </c>
       <c r="N127" s="1"/>
@@ -16210,30 +16567,30 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>13.724600000000001</v>
       </c>
       <c r="W127" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>10.690400000000011</v>
       </c>
       <c r="X127" s="5">
-        <f t="shared" si="31"/>
-        <v>10.690400000000011</v>
-      </c>
-      <c r="Y127" s="5">
         <f t="shared" si="32"/>
         <v>10.690400000000011</v>
       </c>
+      <c r="Y127" s="5">
+        <f t="shared" si="33"/>
+        <v>10.690400000000011</v>
+      </c>
       <c r="Z127" s="5"/>
-      <c r="AA127" s="19"/>
-      <c r="AB127" s="19"/>
+      <c r="AA127" s="1"/>
+      <c r="AB127" s="1"/>
       <c r="AC127" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AD127" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>10.221077481310932</v>
       </c>
       <c r="AE127" s="1">
@@ -16262,14 +16619,17 @@
       </c>
       <c r="AM127" s="1"/>
       <c r="AN127" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11</v>
       </c>
       <c r="AO127" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP127" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP127" s="1">
+        <f t="shared" si="37"/>
+        <v>13.724600000000001</v>
+      </c>
       <c r="AQ127" s="1"/>
       <c r="AR127" s="1"/>
       <c r="AS127" s="1"/>
@@ -16312,11 +16672,11 @@
         <v>983.88499999999999</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-13.261999999999944</v>
       </c>
       <c r="M128" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>970.62300000000005</v>
       </c>
       <c r="N128" s="1"/>
@@ -16332,33 +16692,33 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>194.12460000000002</v>
       </c>
       <c r="W128" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>212.51910000000009</v>
       </c>
       <c r="X128" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>212.51910000000009</v>
       </c>
       <c r="Y128" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>90.363121320000047</v>
       </c>
       <c r="Z128" s="5">
         <f>X128*$Z$1</f>
         <v>122.15597868000005</v>
       </c>
-      <c r="AA128" s="19"/>
-      <c r="AB128" s="19"/>
+      <c r="AA128" s="1"/>
+      <c r="AB128" s="1"/>
       <c r="AC128" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD128" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.9052438485385146</v>
       </c>
       <c r="AE128" s="1">
@@ -16387,14 +16747,17 @@
       </c>
       <c r="AM128" s="1"/>
       <c r="AN128" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>90</v>
       </c>
       <c r="AO128" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>122</v>
       </c>
-      <c r="AP128" s="1"/>
+      <c r="AP128" s="1">
+        <f t="shared" si="37"/>
+        <v>194.12460000000002</v>
+      </c>
       <c r="AQ128" s="1"/>
       <c r="AR128" s="1"/>
       <c r="AS128" s="1"/>
@@ -16435,11 +16798,11 @@
         <v>5</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M129" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5</v>
       </c>
       <c r="N129" s="1"/>
@@ -16453,27 +16816,27 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="W129" s="5"/>
       <c r="X129" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y129" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z129" s="5"/>
-      <c r="AA129" s="19"/>
-      <c r="AB129" s="19"/>
+      <c r="AA129" s="1"/>
+      <c r="AB129" s="1"/>
       <c r="AC129" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>194</v>
       </c>
       <c r="AD129" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>194</v>
       </c>
       <c r="AE129" s="1">
@@ -16504,14 +16867,17 @@
         <v>42</v>
       </c>
       <c r="AN129" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO129" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP129" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP129" s="1">
+        <f t="shared" si="37"/>
+        <v>0.25</v>
+      </c>
       <c r="AQ129" s="1"/>
       <c r="AR129" s="1"/>
       <c r="AS129" s="1"/>
@@ -16553,11 +16919,11 @@
         <v>5</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M130" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5</v>
       </c>
       <c r="N130" s="1"/>
@@ -16571,27 +16937,27 @@
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="W130" s="5"/>
       <c r="X130" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y130" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z130" s="5"/>
-      <c r="AA130" s="19"/>
-      <c r="AB130" s="19"/>
+      <c r="AA130" s="1"/>
+      <c r="AB130" s="1"/>
       <c r="AC130" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>147</v>
       </c>
       <c r="AD130" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>147</v>
       </c>
       <c r="AE130" s="1">
@@ -16622,14 +16988,17 @@
         <v>42</v>
       </c>
       <c r="AN130" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO130" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP130" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP130" s="1">
+        <f t="shared" si="37"/>
+        <v>0.32500000000000001</v>
+      </c>
       <c r="AQ130" s="1"/>
       <c r="AR130" s="1"/>
       <c r="AS130" s="1"/>
@@ -16670,11 +17039,11 @@
         <v>10</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>10</v>
       </c>
       <c r="N131" s="1"/>
@@ -16688,27 +17057,27 @@
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>2</v>
       </c>
       <c r="W131" s="5"/>
       <c r="X131" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y131" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z131" s="5"/>
-      <c r="AA131" s="19"/>
-      <c r="AB131" s="19"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
       <c r="AC131" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>109.5</v>
       </c>
       <c r="AD131" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>109.5</v>
       </c>
       <c r="AE131" s="1">
@@ -16739,14 +17108,17 @@
         <v>42</v>
       </c>
       <c r="AN131" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AO131" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP131" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP131" s="1">
+        <f t="shared" si="37"/>
+        <v>0.5</v>
+      </c>
       <c r="AQ131" s="1"/>
       <c r="AR131" s="1"/>
       <c r="AS131" s="1"/>
@@ -16787,11 +17159,11 @@
         <v>223</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-157</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>66</v>
       </c>
       <c r="N132" s="1"/>
@@ -16807,29 +17179,29 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>13.2</v>
       </c>
       <c r="W132" s="5">
         <v>30</v>
       </c>
       <c r="X132" s="5">
-        <f t="shared" si="31"/>
-        <v>30</v>
-      </c>
-      <c r="Y132" s="5">
         <f t="shared" si="32"/>
         <v>30</v>
       </c>
+      <c r="Y132" s="5">
+        <f t="shared" si="33"/>
+        <v>30</v>
+      </c>
       <c r="Z132" s="5"/>
-      <c r="AA132" s="19"/>
-      <c r="AB132" s="19"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
       <c r="AC132" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20.515151515151516</v>
       </c>
       <c r="AD132" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>18.242424242424246</v>
       </c>
       <c r="AE132" s="1">
@@ -16858,14 +17230,17 @@
       </c>
       <c r="AM132" s="1"/>
       <c r="AN132" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9</v>
       </c>
       <c r="AO132" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP132" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP132" s="1">
+        <f t="shared" si="37"/>
+        <v>3.9599999999999995</v>
+      </c>
       <c r="AQ132" s="1"/>
       <c r="AR132" s="1"/>
       <c r="AS132" s="1"/>
@@ -16906,11 +17281,11 @@
         <v>66</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-20</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>46</v>
       </c>
       <c r="N133" s="1"/>
@@ -16928,29 +17303,29 @@
       </c>
       <c r="U133" s="1"/>
       <c r="V133" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="W133" s="5">
         <v>50</v>
       </c>
       <c r="X133" s="5">
-        <f t="shared" si="31"/>
-        <v>50</v>
-      </c>
-      <c r="Y133" s="5">
         <f t="shared" si="32"/>
         <v>50</v>
       </c>
+      <c r="Y133" s="5">
+        <f t="shared" si="33"/>
+        <v>50</v>
+      </c>
       <c r="Z133" s="5"/>
-      <c r="AA133" s="19"/>
-      <c r="AB133" s="19"/>
+      <c r="AA133" s="1"/>
+      <c r="AB133" s="1"/>
       <c r="AC133" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.8913043478260869</v>
       </c>
       <c r="AD133" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-0.5434782608695653</v>
       </c>
       <c r="AE133" s="1">
@@ -16979,14 +17354,17 @@
       </c>
       <c r="AM133" s="1"/>
       <c r="AN133" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>15</v>
       </c>
       <c r="AO133" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP133" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP133" s="1">
+        <f t="shared" si="37"/>
+        <v>2.76</v>
+      </c>
       <c r="AQ133" s="1"/>
       <c r="AR133" s="1"/>
       <c r="AS133" s="1"/>
@@ -17027,11 +17405,11 @@
         <v>61.35</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" ref="L134:L138" si="49">E134-K134</f>
+        <f t="shared" ref="L134:L138" si="51">E134-K134</f>
         <v>-4.9239999999999995</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" ref="M134:M138" si="50">E134-N134</f>
+        <f t="shared" ref="M134:M138" si="52">E134-N134</f>
         <v>56.426000000000002</v>
       </c>
       <c r="N134" s="1"/>
@@ -17045,30 +17423,30 @@
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>11.2852</v>
       </c>
       <c r="W134" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>28.977399999999975</v>
       </c>
       <c r="X134" s="5">
-        <f t="shared" si="31"/>
-        <v>28.977399999999975</v>
-      </c>
-      <c r="Y134" s="5">
         <f t="shared" si="32"/>
         <v>28.977399999999975</v>
       </c>
+      <c r="Y134" s="5">
+        <f t="shared" si="33"/>
+        <v>28.977399999999975</v>
+      </c>
       <c r="Z134" s="5"/>
-      <c r="AA134" s="19"/>
-      <c r="AB134" s="19"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
       <c r="AC134" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="AD134" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>8.4322652677843575</v>
       </c>
       <c r="AE134" s="1">
@@ -17097,14 +17475,17 @@
       </c>
       <c r="AM134" s="1"/>
       <c r="AN134" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>29</v>
       </c>
       <c r="AO134" s="1">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AP134" s="1"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AP134" s="1">
+        <f t="shared" si="37"/>
+        <v>11.2852</v>
+      </c>
       <c r="AQ134" s="1"/>
       <c r="AR134" s="1"/>
       <c r="AS134" s="1"/>
@@ -17143,11 +17524,11 @@
         <v>32</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-33</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-1</v>
       </c>
       <c r="N135" s="1"/>
@@ -17165,29 +17546,29 @@
       </c>
       <c r="U135" s="1"/>
       <c r="V135" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.2</v>
       </c>
       <c r="W135" s="5">
         <v>20</v>
       </c>
       <c r="X135" s="5">
-        <f t="shared" ref="X135:X138" si="51">W135</f>
+        <f t="shared" ref="X135:X138" si="53">W135</f>
         <v>20</v>
       </c>
       <c r="Y135" s="5">
-        <f t="shared" ref="Y135:Y138" si="52">X135-Z135</f>
+        <f t="shared" ref="Y135:Y138" si="54">X135-Z135</f>
         <v>20</v>
       </c>
       <c r="Z135" s="5"/>
-      <c r="AA135" s="19"/>
-      <c r="AB135" s="19"/>
+      <c r="AA135" s="1"/>
+      <c r="AB135" s="1"/>
       <c r="AC135" s="1">
-        <f t="shared" ref="AC135:AC138" si="53">(F135+O135+P135+Q135+R135+S135+T135+U135+X135)/V135</f>
+        <f t="shared" ref="AC135:AC138" si="55">(F135+O135+P135+Q135+R135+S135+T135+U135+X135)/V135</f>
         <v>-165</v>
       </c>
       <c r="AD135" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-65</v>
       </c>
       <c r="AE135" s="1">
@@ -17216,14 +17597,17 @@
       </c>
       <c r="AM135" s="1"/>
       <c r="AN135" s="1">
-        <f t="shared" ref="AN135:AN138" si="54">ROUND(G135*Y135,0)</f>
+        <f t="shared" ref="AN135:AN138" si="56">ROUND(G135*Y135,0)</f>
         <v>6</v>
       </c>
       <c r="AO135" s="1">
-        <f t="shared" ref="AO135:AO138" si="55">ROUND(G135*Z135,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP135" s="1"/>
+        <f t="shared" ref="AO135:AO138" si="57">ROUND(G135*Z135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP135" s="1">
+        <f t="shared" ref="AP135:AP138" si="58">V135*G135</f>
+        <v>-0.06</v>
+      </c>
       <c r="AQ135" s="1"/>
       <c r="AR135" s="1"/>
       <c r="AS135" s="1"/>
@@ -17264,11 +17648,11 @@
         <v>55</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-13</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>42</v>
       </c>
       <c r="N136" s="1"/>
@@ -17284,27 +17668,27 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>8.4</v>
       </c>
       <c r="W136" s="5"/>
       <c r="X136" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Y136" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Z136" s="5"/>
-      <c r="AA136" s="19"/>
-      <c r="AB136" s="19"/>
+      <c r="AA136" s="1"/>
+      <c r="AB136" s="1"/>
       <c r="AC136" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>19.523809523809522</v>
       </c>
       <c r="AD136" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>19.523809523809522</v>
       </c>
       <c r="AE136" s="1">
@@ -17333,14 +17717,17 @@
       </c>
       <c r="AM136" s="1"/>
       <c r="AN136" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AO136" s="1">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AP136" s="1"/>
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AP136" s="1">
+        <f t="shared" si="58"/>
+        <v>1.008</v>
+      </c>
       <c r="AQ136" s="1"/>
       <c r="AR136" s="1"/>
       <c r="AS136" s="1"/>
@@ -17381,11 +17768,11 @@
         <v>67</v>
       </c>
       <c r="L137" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-15</v>
       </c>
       <c r="M137" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>52</v>
       </c>
       <c r="N137" s="11"/>
@@ -17399,27 +17786,27 @@
       <c r="T137" s="11"/>
       <c r="U137" s="11"/>
       <c r="V137" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>10.4</v>
       </c>
       <c r="W137" s="13"/>
       <c r="X137" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Y137" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Z137" s="5"/>
-      <c r="AA137" s="20"/>
-      <c r="AB137" s="19"/>
+      <c r="AA137" s="11"/>
+      <c r="AB137" s="1"/>
       <c r="AC137" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>6.5384615384615383</v>
       </c>
       <c r="AD137" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>6.5384615384615383</v>
       </c>
       <c r="AE137" s="11">
@@ -17448,14 +17835,17 @@
       </c>
       <c r="AM137" s="11"/>
       <c r="AN137" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AO137" s="1">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AP137" s="1"/>
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AP137" s="1">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
       <c r="AQ137" s="1"/>
       <c r="AR137" s="1"/>
       <c r="AS137" s="1"/>
@@ -17492,11 +17882,11 @@
         <v>1</v>
       </c>
       <c r="L138" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-1</v>
       </c>
       <c r="M138" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="N138" s="11"/>
@@ -17510,27 +17900,27 @@
       <c r="T138" s="11"/>
       <c r="U138" s="11"/>
       <c r="V138" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="W138" s="13"/>
       <c r="X138" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Y138" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Z138" s="5"/>
-      <c r="AA138" s="20"/>
-      <c r="AB138" s="19"/>
+      <c r="AA138" s="11"/>
+      <c r="AB138" s="1"/>
       <c r="AC138" s="1" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD138" s="11" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE138" s="11">
@@ -17559,14 +17949,17 @@
       </c>
       <c r="AM138" s="11"/>
       <c r="AN138" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AO138" s="1">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AP138" s="1"/>
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AP138" s="1">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
       <c r="AQ138" s="1"/>
       <c r="AR138" s="1"/>
       <c r="AS138" s="1"/>
